--- a/Verbesserungsliste.xlsx
+++ b/Verbesserungsliste.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hanna\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hanna\Documents\Master\Industrierobotik Optimierung\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D66B7A8E-1F56-45DA-80CE-1B87BEA53DBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43675EEA-2DEE-4D04-AB29-BC790EF2927A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="80">
   <si>
     <t>Nr.</t>
   </si>
@@ -233,6 +233,33 @@
   </si>
   <si>
     <t>Not started</t>
+  </si>
+  <si>
+    <t>LichtschranKe weiter nach vorne</t>
+  </si>
+  <si>
+    <t>Kamera muss früher auslösen</t>
+  </si>
+  <si>
+    <t>Kamera Befestigung</t>
+  </si>
+  <si>
+    <t>Kamera im Turm wackelt</t>
+  </si>
+  <si>
+    <t>Koordinatensystem im Kameraturm</t>
+  </si>
+  <si>
+    <t>zu undeutlich</t>
+  </si>
+  <si>
+    <t>Elektrik Aufbau 1.0</t>
+  </si>
+  <si>
+    <t>Elektrik Aufbau 2.0</t>
+  </si>
+  <si>
+    <t>Elektrik überarbeiten</t>
   </si>
 </sst>
 </file>
@@ -311,7 +338,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -319,10 +346,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -335,7 +359,35 @@
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="28">
+  <dxfs count="7">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -363,190 +415,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8"/>
         </patternFill>
       </fill>
     </dxf>
@@ -850,17 +718,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="26.265625" customWidth="1"/>
+    <col min="2" max="2" width="31.9296875" customWidth="1"/>
     <col min="3" max="3" width="60.1328125" customWidth="1"/>
     <col min="4" max="4" width="10.53125" customWidth="1"/>
     <col min="5" max="5" width="19.265625" customWidth="1"/>
     <col min="6" max="6" width="9.46484375" customWidth="1"/>
-    <col min="7" max="7" width="9.06640625" style="6"/>
-    <col min="8" max="8" width="11.6640625" style="6" customWidth="1"/>
+    <col min="7" max="7" width="9.06640625" style="5"/>
+    <col min="8" max="8" width="11.6640625" style="5" customWidth="1"/>
     <col min="9" max="9" width="26.86328125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -877,19 +745,19 @@
       <c r="D1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>66</v>
       </c>
     </row>
@@ -912,7 +780,7 @@
       <c r="F2">
         <v>2</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -935,7 +803,7 @@
       <c r="F3">
         <v>1</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -958,7 +826,7 @@
       <c r="F4">
         <v>2</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="5" t="s">
         <v>32</v>
       </c>
       <c r="I4" t="s">
@@ -984,7 +852,7 @@
       <c r="F5">
         <v>3</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="5" t="s">
         <v>32</v>
       </c>
       <c r="I5" t="s">
@@ -1010,7 +878,7 @@
       <c r="F6">
         <v>2</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="5" t="s">
         <v>32</v>
       </c>
       <c r="I6" t="s">
@@ -1036,7 +904,7 @@
       <c r="F7">
         <v>1</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="5" t="s">
         <v>32</v>
       </c>
       <c r="I7" t="s">
@@ -1062,7 +930,7 @@
       <c r="F8">
         <v>1</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1085,7 +953,7 @@
       <c r="F9">
         <v>2</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="5" t="s">
         <v>32</v>
       </c>
       <c r="I9" t="s">
@@ -1111,7 +979,7 @@
       <c r="F10">
         <v>3</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="H10" s="5" t="s">
         <v>32</v>
       </c>
       <c r="I10" t="s">
@@ -1137,7 +1005,7 @@
       <c r="F11">
         <v>3</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="H11" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1160,7 +1028,7 @@
       <c r="F12">
         <v>1</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1183,7 +1051,7 @@
       <c r="F13">
         <v>2</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1206,7 +1074,7 @@
       <c r="F14">
         <v>2</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="5" t="s">
         <v>32</v>
       </c>
       <c r="I14" t="s">
@@ -1224,7 +1092,7 @@
         <v>27</v>
       </c>
       <c r="D15" t="s">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="E15" t="s">
         <v>45</v>
@@ -1232,7 +1100,7 @@
       <c r="F15">
         <v>2</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1247,7 +1115,7 @@
         <v>37</v>
       </c>
       <c r="D16" t="s">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="E16" t="s">
         <v>45</v>
@@ -1255,7 +1123,7 @@
       <c r="F16">
         <v>2</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" s="5" t="s">
         <v>32</v>
       </c>
       <c r="I16" t="s">
@@ -1267,21 +1135,21 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>16</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="D17" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="E17" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="G17" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1290,25 +1158,22 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>79</v>
       </c>
       <c r="D18" t="s">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="E18" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F18">
-        <v>3</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" t="s">
-        <v>47</v>
+        <v>1</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.45">
@@ -1316,21 +1181,21 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="C19" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="D19" t="s">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="E19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F19">
-        <v>2</v>
-      </c>
-      <c r="G19" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G19" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1339,90 +1204,184 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" t="s">
+        <v>70</v>
+      </c>
+      <c r="E20" t="s">
+        <v>56</v>
+      </c>
+      <c r="F20">
+        <v>3</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" t="s">
+        <v>65</v>
+      </c>
+      <c r="D21" t="s">
+        <v>70</v>
+      </c>
+      <c r="E21" t="s">
+        <v>35</v>
+      </c>
+      <c r="F21">
+        <v>2</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
         <v>49</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C22" t="s">
         <v>50</v>
       </c>
-      <c r="D20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F20">
+      <c r="D22" t="s">
+        <v>70</v>
+      </c>
+      <c r="E22" t="s">
+        <v>56</v>
+      </c>
+      <c r="F22">
         <v>2</v>
       </c>
-      <c r="G20" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="B22" t="s">
-        <v>51</v>
+      <c r="G22" s="5" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A23">
+        <v>22</v>
+      </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="C23" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="B26" t="s">
-        <v>54</v>
-      </c>
-      <c r="C26" t="s">
-        <v>35</v>
+        <v>72</v>
+      </c>
+      <c r="D23" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" t="s">
+        <v>74</v>
+      </c>
+      <c r="D24" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" t="s">
+        <v>76</v>
+      </c>
+      <c r="D25" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C27" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="B31" t="s">
+        <v>54</v>
+      </c>
+      <c r="C31" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="B32" t="s">
+        <v>55</v>
+      </c>
+      <c r="C32" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B33" t="s">
         <v>58</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C33" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="B29" t="s">
+    <row r="34" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B34" t="s">
         <v>57</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C34" t="s">
         <v>45</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="D1:D1048576">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
+      <formula>$D$3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
+      <formula>"In progress"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
+      <formula>"Done"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E1:E1048576">
-    <cfRule type="containsText" dxfId="12" priority="7" operator="containsText" text="Thomas">
-      <formula>NOT(ISERROR(SEARCH("Thomas",E1)))</formula>
+    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Oskar">
+      <formula>NOT(ISERROR(SEARCH("Oskar",E1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="6" operator="containsText" text="Oliver">
+    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="Hannah">
+      <formula>NOT(ISERROR(SEARCH("Hannah",E1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="6" operator="containsText" text="Oliver">
       <formula>NOT(ISERROR(SEARCH("Oliver",E1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="5" operator="containsText" text="Hannah">
-      <formula>NOT(ISERROR(SEARCH("Hannah",E1)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="4" operator="containsText" text="Oskar">
-      <formula>NOT(ISERROR(SEARCH("Oskar",E1)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
-      <formula>"Done"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>"In progress"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
-      <formula>$D$3</formula>
+    <cfRule type="containsText" dxfId="0" priority="7" operator="containsText" text="Thomas">
+      <formula>NOT(ISERROR(SEARCH("Thomas",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Verbesserungsliste.xlsx
+++ b/Verbesserungsliste.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hanna\Documents\Master\Industrierobotik Optimierung\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\neume\Desktop\MCI\Robotik_Projekt\Optimierung-Laboraufgabe-Robotik\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43675EEA-2DEE-4D04-AB29-BC790EF2927A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{521C72C3-306C-4850-8E91-A535E7B763A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="111">
   <si>
     <t>Nr.</t>
   </si>
@@ -49,9 +49,6 @@
     <t>Ethernet-Ports</t>
   </si>
   <si>
-    <t>Kamera-Turm</t>
-  </si>
-  <si>
     <t>Metallrand Fließband</t>
   </si>
   <si>
@@ -91,9 +88,6 @@
     <t>Zwei zusätzliche Ports für Roboteranbindung</t>
   </si>
   <si>
-    <t>Innen weiß zur Lichtverteilung, ab Mitte zweifarbig drucken</t>
-  </si>
-  <si>
     <t>Nur ein Roboter betriebsbereit, neuer 5-pol Stecker benötigt</t>
   </si>
   <si>
@@ -151,9 +145,6 @@
     <t>drei getrennte Kabel, Beschriftung, Anleitung</t>
   </si>
   <si>
-    <t>erst ausprobieren</t>
-  </si>
-  <si>
     <t>Angebote einholen für das Gegenstück aus Alu (Xometry), erst testen mit 3D-Druck</t>
   </si>
   <si>
@@ -260,6 +251,108 @@
   </si>
   <si>
     <t>Elektrik überarbeiten</t>
+  </si>
+  <si>
+    <t>Cognex Funktionen zur Umsetzung erklären</t>
+  </si>
+  <si>
+    <t>Cognex Kalibrierung (pdf mit Grid) (Video)</t>
+  </si>
+  <si>
+    <t>Cognex: Wie wird der Abstand und der Winkel gemessen</t>
+  </si>
+  <si>
+    <t>Testbilder mit Ergebnissen (Im Namen)</t>
+  </si>
+  <si>
+    <t>Cognex-ABB Funktion integration</t>
+  </si>
+  <si>
+    <t>minimaler Cognex Job mit der Übergabe der Zufallszahlen</t>
+  </si>
+  <si>
+    <t>minimal Rapid-Programm erklären (IP eintragen, get string, load job usw.)</t>
+  </si>
+  <si>
+    <t>Tipps geben was im Cognex-Job übertragen werden sollte</t>
+  </si>
+  <si>
+    <t>Text und Bilder: wie soll der Aufbau auf dem Tisch ausschauen</t>
+  </si>
+  <si>
+    <t>Welche Stecker müssen wo eingesteckt werden</t>
+  </si>
+  <si>
+    <t>"Schaltplan zum anstecken"</t>
+  </si>
+  <si>
+    <t>RAPID-Modul Conveyor: Funktionen erklären incl. Mwe</t>
+  </si>
+  <si>
+    <t>I/O Steuerung der Conveyor über den Controller</t>
+  </si>
+  <si>
+    <t>Wo findet man welche Variablen (Conveyor Tracking, z.B. c1softsync)</t>
+  </si>
+  <si>
+    <t>Counts per Meter (Hinweis zum notwendigem Python-Skript)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Counts per Meter Video und Text dazu </t>
+  </si>
+  <si>
+    <t>ConveyorBaseFrame Video und Text dazu</t>
+  </si>
+  <si>
+    <t>Minimal working example (Conveyor Tracking)</t>
+  </si>
+  <si>
+    <t>Zweiter Roboter muss lauffähig gemacht werden</t>
+  </si>
+  <si>
+    <t>Text (Liste) schreiben im Sakai</t>
+  </si>
+  <si>
+    <t>Video (Bildschirmaufnahme)</t>
+  </si>
+  <si>
+    <t>PowerPoint Erklärung mit Foto</t>
+  </si>
+  <si>
+    <t>Vor Ort aufnehmen</t>
+  </si>
+  <si>
+    <t>Video (Bildschirmaufnahme) und Text</t>
+  </si>
+  <si>
+    <t>Video</t>
+  </si>
+  <si>
+    <t>Text und Fotos</t>
+  </si>
+  <si>
+    <t>Fotos und in PowerPoint bearbeiten</t>
+  </si>
+  <si>
+    <t>PowerPoint</t>
+  </si>
+  <si>
+    <t>Text</t>
+  </si>
+  <si>
+    <t>Text bzw. Bildschirmfotos vom TeachPanel</t>
+  </si>
+  <si>
+    <t>Video während der Kalbrierung im Labor und Text im Sakai</t>
+  </si>
+  <si>
+    <t>Video während der Kalbrierung im Labor dazu im Sakai</t>
+  </si>
+  <si>
+    <t>Code bzw. Text im Sakai</t>
+  </si>
+  <si>
+    <t>_____</t>
   </si>
 </sst>
 </file>
@@ -718,21 +811,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:I59"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="31.9296875" customWidth="1"/>
-    <col min="3" max="3" width="60.1328125" customWidth="1"/>
-    <col min="4" max="4" width="10.53125" customWidth="1"/>
-    <col min="5" max="5" width="19.265625" customWidth="1"/>
-    <col min="6" max="6" width="9.46484375" customWidth="1"/>
-    <col min="7" max="7" width="9.06640625" style="5"/>
-    <col min="8" max="8" width="11.6640625" style="5" customWidth="1"/>
-    <col min="9" max="9" width="26.86328125" customWidth="1"/>
+    <col min="1" max="1" width="6.08984375" customWidth="1"/>
+    <col min="2" max="2" width="62.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="60.08984375" customWidth="1"/>
+    <col min="4" max="4" width="10.54296875" customWidth="1"/>
+    <col min="5" max="5" width="19.26953125" customWidth="1"/>
+    <col min="6" max="6" width="9.453125" customWidth="1"/>
+    <col min="7" max="7" width="9.08984375" style="5"/>
+    <col min="8" max="8" width="11.6328125" style="5" customWidth="1"/>
+    <col min="9" max="9" width="26.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -743,25 +836,25 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -769,22 +862,22 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F2">
         <v>2</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -792,22 +885,22 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -815,51 +908,51 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F4">
         <v>2</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F5">
         <v>3</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -867,25 +960,25 @@
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D6" t="s">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F6">
         <v>2</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -893,48 +986,48 @@
         <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="E7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -942,25 +1035,25 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D9" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="E9" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F9">
         <v>2</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -968,25 +1061,22 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="D10" t="s">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="E10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F10">
         <v>3</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -994,22 +1084,22 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>67</v>
+        <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F11">
-        <v>3</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+        <v>1</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1017,22 +1107,22 @@
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D12" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E12" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1040,22 +1130,25 @@
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" t="s">
         <v>33</v>
-      </c>
-      <c r="E13" t="s">
-        <v>35</v>
       </c>
       <c r="F13">
         <v>2</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
+        <v>30</v>
+      </c>
+      <c r="I13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1063,25 +1156,22 @@
         <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D14" t="s">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="E14" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="F14">
         <v>2</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I14" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1089,94 +1179,94 @@
         <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="D15" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E15" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F15">
         <v>2</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+        <v>30</v>
+      </c>
+      <c r="I15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="D16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E16" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D17" t="s">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="E17" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>79</v>
+        <v>26</v>
       </c>
       <c r="D18" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E18" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="F18">
         <v>1</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1184,184 +1274,469 @@
         <v>16</v>
       </c>
       <c r="C19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E19" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="F19">
-        <v>1</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
+        <v>3</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="D20" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="E20" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="F20">
-        <v>3</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
+        <v>2</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C21" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="D21" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E21" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="F21">
         <v>2</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="C22" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="D22" t="s">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="E22" t="s">
-        <v>56</v>
-      </c>
-      <c r="F22">
-        <v>2</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23" t="s">
         <v>71</v>
       </c>
-      <c r="C23" t="s">
-        <v>72</v>
-      </c>
       <c r="D23" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+      <c r="E23" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" t="s">
         <v>73</v>
       </c>
-      <c r="C24" t="s">
-        <v>74</v>
-      </c>
       <c r="D24" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
+        <v>31</v>
+      </c>
+      <c r="E24" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C25" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="D25" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>78</v>
+      </c>
+      <c r="C26" t="s">
+        <v>97</v>
+      </c>
+      <c r="D26" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>26</v>
+      </c>
       <c r="B27" t="s">
+        <v>79</v>
+      </c>
+      <c r="C27" t="s">
+        <v>98</v>
+      </c>
+      <c r="D27" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>80</v>
+      </c>
+      <c r="C28" t="s">
+        <v>99</v>
+      </c>
+      <c r="D28" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>81</v>
+      </c>
+      <c r="C29" t="s">
+        <v>97</v>
+      </c>
+      <c r="D29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>82</v>
+      </c>
+      <c r="C30" t="s">
+        <v>100</v>
+      </c>
+      <c r="D30" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>83</v>
+      </c>
+      <c r="C31" t="s">
+        <v>101</v>
+      </c>
+      <c r="D31" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>84</v>
+      </c>
+      <c r="C32" t="s">
+        <v>96</v>
+      </c>
+      <c r="D32" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>85</v>
+      </c>
+      <c r="C33" t="s">
+        <v>102</v>
+      </c>
+      <c r="D33" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>86</v>
+      </c>
+      <c r="C34" t="s">
+        <v>103</v>
+      </c>
+      <c r="D34" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>87</v>
+      </c>
+      <c r="C35" t="s">
+        <v>104</v>
+      </c>
+      <c r="D35" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>88</v>
+      </c>
+      <c r="C36" t="s">
+        <v>101</v>
+      </c>
+      <c r="D36" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>89</v>
+      </c>
+      <c r="C37" t="s">
+        <v>106</v>
+      </c>
+      <c r="D37" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>90</v>
+      </c>
+      <c r="C38" t="s">
+        <v>106</v>
+      </c>
+      <c r="D38" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>91</v>
+      </c>
+      <c r="C39" t="s">
+        <v>105</v>
+      </c>
+      <c r="D39" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>92</v>
+      </c>
+      <c r="C40" t="s">
+        <v>107</v>
+      </c>
+      <c r="D40" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>93</v>
+      </c>
+      <c r="C41" t="s">
+        <v>108</v>
+      </c>
+      <c r="D41" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>94</v>
+      </c>
+      <c r="C42" t="s">
+        <v>109</v>
+      </c>
+      <c r="D42" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>95</v>
+      </c>
+      <c r="C43" t="s">
+        <v>110</v>
+      </c>
+      <c r="D43" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>33</v>
+      </c>
+      <c r="B52" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>34</v>
+      </c>
+      <c r="B53" t="s">
+        <v>49</v>
+      </c>
+      <c r="C53" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>37</v>
+      </c>
+      <c r="B56" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="B28" t="s">
+      <c r="C56" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>38</v>
+      </c>
+      <c r="B57" t="s">
         <v>52</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C57" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="B31" t="s">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>39</v>
+      </c>
+      <c r="B58" t="s">
+        <v>55</v>
+      </c>
+      <c r="C58" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>40</v>
+      </c>
+      <c r="B59" t="s">
         <v>54</v>
       </c>
-      <c r="C31" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="B32" t="s">
-        <v>55</v>
-      </c>
-      <c r="C32" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B33" t="s">
-        <v>58</v>
-      </c>
-      <c r="C33" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B34" t="s">
-        <v>57</v>
-      </c>
-      <c r="C34" t="s">
-        <v>45</v>
+      <c r="C59" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1:D1048576">
     <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
-      <formula>$D$3</formula>
+      <formula>"Not started"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
       <formula>"In progress"</formula>

--- a/Verbesserungsliste.xlsx
+++ b/Verbesserungsliste.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\neume\Desktop\MCI\Robotik_Projekt\Optimierung-Laboraufgabe-Robotik\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{521C72C3-306C-4850-8E91-A535E7B763A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61480ECB-F542-41A5-BB0F-119DD967C47A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22290" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="181">
   <si>
     <t>Nr.</t>
   </si>
@@ -106,9 +107,6 @@
     <t>Beschriftung außen ergänzen</t>
   </si>
   <si>
-    <t>NPN-LED durch größere PNP-LED ersetzen, Loch bohren, LED anschließen</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
@@ -166,15 +164,6 @@
     <t>CountsPerMeter, ConveyorBaseFrame, Mininmal working example</t>
   </si>
   <si>
-    <t>Version 2.1</t>
-  </si>
-  <si>
-    <t>Zuführförderband und Conveyor als ein Teil</t>
-  </si>
-  <si>
-    <t>Kabelführung überdenken</t>
-  </si>
-  <si>
     <t>3D Druck</t>
   </si>
   <si>
@@ -353,13 +342,235 @@
   </si>
   <si>
     <t>_____</t>
+  </si>
+  <si>
+    <t>E-Durchführung Abdeckung und Verkabelung</t>
+  </si>
+  <si>
+    <t>Am Roboter</t>
+  </si>
+  <si>
+    <t>Zeitaufwand</t>
+  </si>
+  <si>
+    <t>2h</t>
+  </si>
+  <si>
+    <t>NPN-LED durch größere PNP-LED ersetzen, Loch bohren</t>
+  </si>
+  <si>
+    <t>1h</t>
+  </si>
+  <si>
+    <t>3,5h</t>
+  </si>
+  <si>
+    <t>1,5h</t>
+  </si>
+  <si>
+    <t>COGNEX-Anleitung</t>
+  </si>
+  <si>
+    <t>Aufbau Anleitung</t>
+  </si>
+  <si>
+    <t>Conveyor-Tracking Anleitung</t>
+  </si>
+  <si>
+    <t>Zweiter Roboter Aufbau</t>
+  </si>
+  <si>
+    <t>Drucken, Montieren, Verkabeln</t>
+  </si>
+  <si>
+    <t>Abdeckungen + LED</t>
+  </si>
+  <si>
+    <t>Innen weiß lackieren? Einfacher als Multimaterial-Druck</t>
+  </si>
+  <si>
+    <t>Kameraturm</t>
+  </si>
+  <si>
+    <t>Verbessertes Montagesystem umsetzen</t>
+  </si>
+  <si>
+    <t>Teaching-Tools?</t>
+  </si>
+  <si>
+    <t>Neu verkabeln, wie beim Zweitaufbau</t>
+  </si>
+  <si>
+    <t>Verkabelung</t>
+  </si>
+  <si>
+    <t>Löcher ETH/M12 Ports, Überstand oben abschneiden</t>
+  </si>
+  <si>
+    <t>Blechbearbeitung</t>
+  </si>
+  <si>
+    <t>Neue Version drucken und austauschen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rutsche </t>
+  </si>
+  <si>
+    <t>Kameraturm Base</t>
+  </si>
+  <si>
+    <t>To-Dos zur Verbesserung Erstaufbau</t>
+  </si>
+  <si>
+    <t>Detailliert, so effektiv wie möglich das Gerät übergeben</t>
+  </si>
+  <si>
+    <t>DOKU</t>
+  </si>
+  <si>
+    <t>Inbetriebnahme</t>
+  </si>
+  <si>
+    <t>Eloxieren inkl Demontage + Montage</t>
+  </si>
+  <si>
+    <t>Sind alle Blechteile bereit und fehlerfrei?</t>
+  </si>
+  <si>
+    <t>Konstruktion checken</t>
+  </si>
+  <si>
+    <t>Testen ob keine Teile mehr hängen bleiben</t>
+  </si>
+  <si>
+    <t>Rutsche testen</t>
+  </si>
+  <si>
+    <t>Beschriftungen drucken, um Layout zu testen</t>
+  </si>
+  <si>
+    <t>Labels außen</t>
+  </si>
+  <si>
+    <t>Gewinde Nieten besorgen</t>
+  </si>
+  <si>
+    <t>SPS Abdeckung von außen, 4 Löcher, 5mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plexi Abdeckung </t>
+  </si>
+  <si>
+    <t>Ersten Druck behalten, erst wenn alles fertig ist neu drucken</t>
+  </si>
+  <si>
+    <t>Misumi für TCP-Spitze, lange Alu-Spitze verwerfen</t>
+  </si>
+  <si>
+    <t>Drucken, Spitze drehen, evtl. Verbessern?!</t>
+  </si>
+  <si>
+    <t>Teaching-Tools 2. Greifer</t>
+  </si>
+  <si>
+    <t>Ausbaustufe: Harting-Stecker</t>
+  </si>
+  <si>
+    <t>Konstruktion + 3D-Druck ausstehend</t>
+  </si>
+  <si>
+    <t>Kabeldurchführung Abdeckung</t>
+  </si>
+  <si>
+    <t>Polarität in der Doku aufnehmen</t>
+  </si>
+  <si>
+    <t>Teileträger mit Magneten versehen (Polarität!!) und am Förderband verschrauben</t>
+  </si>
+  <si>
+    <t>3D-Druck restliche Teileträger + Montage</t>
+  </si>
+  <si>
+    <t>Kameraturm + Kamera-Halterung drucken, Kamera-Halterung in CAD verstärken, innen weiß lackieren</t>
+  </si>
+  <si>
+    <t>3D-Druck Kameraturm</t>
+  </si>
+  <si>
+    <t>SPS-Halterung nach oben versetzen – Zwischenadapter lasern</t>
+  </si>
+  <si>
+    <t>Normales Kabel wird geknickt, da wenig Platz under der SPS vorhanden ist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAN Flachbandkabel für SPS </t>
+  </si>
+  <si>
+    <t>M12 5-Pin Kabel vom Förderband zum Roboterschaltschrank: pin 5 ist noch frei -&gt; zu Pin 9 an Tracking-Karte legen</t>
+  </si>
+  <si>
+    <t>Trigger-Port 2. Roboter Check</t>
+  </si>
+  <si>
+    <t>WLAN ausbauen – alles kabelgebunden final</t>
+  </si>
+  <si>
+    <t>Offen</t>
+  </si>
+  <si>
+    <t>SPS Verbindung einstellen</t>
+  </si>
+  <si>
+    <t>WLAN 2. Roboter Check</t>
+  </si>
+  <si>
+    <t>Verkabelung fertig, Inbetriebnahme OK, Funktionscheck ausstehend</t>
+  </si>
+  <si>
+    <t>SPS Check</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>Pins und Stecker sind vorhanden, Christian Nagl SCHMALZ bringt heute den zweiten Flansch</t>
+  </si>
+  <si>
+    <t>E-Durchführung Schnellwechsler</t>
+  </si>
+  <si>
+    <t>To-Dos zur Fertigstellung Zweitaufbau</t>
+  </si>
+  <si>
+    <t>Olli</t>
+  </si>
+  <si>
+    <t>Offen lassen</t>
+  </si>
+  <si>
+    <t>Alle</t>
+  </si>
+  <si>
+    <t>Lösbar mittels richtigen CognexEinstellungen</t>
+  </si>
+  <si>
+    <t>Thomas/Olli</t>
+  </si>
+  <si>
+    <t>Zweiter Aufbau erst testen, dann drucken</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Offen lassen </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -374,6 +585,26 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -428,10 +659,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -448,11 +680,126 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard 2" xfId="1" xr:uid="{C5473660-9688-436F-8071-2AEA31843F41}"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="17">
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FF9C5700"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FF9C0006"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -511,6 +858,31 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -522,6 +894,25 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{ADF0C628-87B5-4E6D-A20A-A83A20831158}" name="Tabelle1" displayName="Tabelle1" ref="A1:J48" totalsRowShown="0" headerRowDxfId="14">
+  <autoFilter ref="A1:J48" xr:uid="{ADF0C628-87B5-4E6D-A20A-A83A20831158}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{05561CB3-D66F-4B3A-834B-EF02D87D9FD6}" name="Nr."/>
+    <tableColumn id="2" xr3:uid="{F7DCFBA3-13FF-4C7B-8BF5-F13C6266F0A2}" name="Thema"/>
+    <tableColumn id="3" xr3:uid="{574A6884-6A4F-4958-B5B5-BA2D1F8387B2}" name="Beschreibung"/>
+    <tableColumn id="4" xr3:uid="{1E048EE8-98F7-43F9-9AC7-731BBEA2137B}" name="Status"/>
+    <tableColumn id="5" xr3:uid="{FA5A1335-E3E8-486B-83D1-5FF8ADEE52FA}" name="Verantwortlicher"/>
+    <tableColumn id="6" xr3:uid="{58BEAA5F-C6AD-4B13-BF34-4D565CC30F12}" name="Zeitaufwand"/>
+    <tableColumn id="7" xr3:uid="{B1B773FB-CBCD-4944-824A-E682569C730B}" name="Priorität"/>
+    <tableColumn id="8" xr3:uid="{1A2614E9-A6B9-421C-B8C6-2E52C63CD053}" name="Pflicht" dataDxfId="16"/>
+    <tableColumn id="9" xr3:uid="{F8040B49-6F6B-472D-BBAE-CD038BF42272}" name="Nice to have" dataDxfId="15"/>
+    <tableColumn id="10" xr3:uid="{3C27D6E3-F773-4132-81C4-6F24859D6E70}" name="Benjamins Kommentare"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -811,21 +1202,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I59"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:J63"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.08984375" customWidth="1"/>
+    <col min="1" max="1" width="6.1796875" customWidth="1"/>
     <col min="2" max="2" width="62.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="60.08984375" customWidth="1"/>
+    <col min="3" max="3" width="60.1796875" customWidth="1"/>
     <col min="4" max="4" width="10.54296875" customWidth="1"/>
-    <col min="5" max="5" width="19.26953125" customWidth="1"/>
-    <col min="6" max="6" width="9.453125" customWidth="1"/>
-    <col min="7" max="7" width="9.08984375" style="5"/>
-    <col min="8" max="8" width="11.6328125" style="5" customWidth="1"/>
-    <col min="9" max="9" width="26.81640625" customWidth="1"/>
+    <col min="5" max="6" width="19.26953125" customWidth="1"/>
+    <col min="7" max="7" width="9.81640625" customWidth="1"/>
+    <col min="8" max="8" width="9.1796875" style="5"/>
+    <col min="9" max="9" width="13.1796875" style="5" customWidth="1"/>
+    <col min="10" max="10" width="26.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -836,25 +1227,28 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G1" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J1" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -862,22 +1256,25 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F2">
+        <v>32</v>
+      </c>
+      <c r="F2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G2">
         <v>2</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H2" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -888,19 +1285,19 @@
         <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3">
+        <v>33</v>
+      </c>
+      <c r="G3">
         <v>1</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H3" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -911,48 +1308,51 @@
         <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F4">
+        <v>32</v>
+      </c>
+      <c r="F4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G4">
         <v>2</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="I4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F5">
+        <v>41</v>
+      </c>
+      <c r="G5">
         <v>3</v>
       </c>
-      <c r="H5" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -960,25 +1360,28 @@
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6">
+        <v>32</v>
+      </c>
+      <c r="F6" t="s">
+        <v>113</v>
+      </c>
+      <c r="G6">
         <v>2</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -989,45 +1392,45 @@
         <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s">
-        <v>53</v>
-      </c>
-      <c r="F7">
+        <v>49</v>
+      </c>
+      <c r="G7">
         <v>1</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C8" t="s">
         <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8">
+        <v>33</v>
+      </c>
+      <c r="G8">
         <v>1</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H8" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1038,22 +1441,22 @@
         <v>21</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E9" t="s">
-        <v>53</v>
-      </c>
-      <c r="F9">
+        <v>49</v>
+      </c>
+      <c r="G9">
         <v>2</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="I9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1061,22 +1464,25 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10">
+        <v>32</v>
+      </c>
+      <c r="F10" t="s">
+        <v>114</v>
+      </c>
+      <c r="G10">
         <v>3</v>
       </c>
-      <c r="H10" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I10" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1087,19 +1493,19 @@
         <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E11" t="s">
-        <v>34</v>
-      </c>
-      <c r="F11">
+        <v>33</v>
+      </c>
+      <c r="G11">
         <v>1</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H11" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1110,19 +1516,22 @@
         <v>23</v>
       </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
         <v>2</v>
       </c>
-      <c r="G12" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H12" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1133,22 +1542,25 @@
         <v>24</v>
       </c>
       <c r="D13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E13" t="s">
-        <v>33</v>
-      </c>
-      <c r="F13">
+        <v>32</v>
+      </c>
+      <c r="F13" t="s">
+        <v>110</v>
+      </c>
+      <c r="G13">
         <v>2</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="I13" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H13" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1159,19 +1571,19 @@
         <v>25</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E14" t="s">
-        <v>42</v>
-      </c>
-      <c r="F14">
+        <v>41</v>
+      </c>
+      <c r="G14">
         <v>2</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H14" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1179,71 +1591,71 @@
         <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E15" t="s">
+        <v>41</v>
+      </c>
+      <c r="G15">
+        <v>2</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J15" t="s">
         <v>42</v>
       </c>
-      <c r="F15">
-        <v>2</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="I15" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C16" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E16" t="s">
-        <v>42</v>
-      </c>
-      <c r="F16">
+        <v>41</v>
+      </c>
+      <c r="G16">
         <v>1</v>
       </c>
-      <c r="G16" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H16" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E17" t="s">
-        <v>42</v>
-      </c>
-      <c r="F17">
+        <v>41</v>
+      </c>
+      <c r="G17">
         <v>1</v>
       </c>
-      <c r="G17" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H17" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1254,19 +1666,19 @@
         <v>26</v>
       </c>
       <c r="D18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E18" t="s">
-        <v>34</v>
-      </c>
-      <c r="F18">
+        <v>33</v>
+      </c>
+      <c r="G18">
         <v>1</v>
       </c>
-      <c r="G18" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H18" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1277,466 +1689,1104 @@
         <v>27</v>
       </c>
       <c r="D19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E19" t="s">
-        <v>53</v>
-      </c>
-      <c r="F19">
+        <v>49</v>
+      </c>
+      <c r="G19">
         <v>3</v>
       </c>
-      <c r="H19" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="I19" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I19" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J19" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D20" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" t="s">
         <v>32</v>
       </c>
-      <c r="E20" t="s">
-        <v>33</v>
-      </c>
-      <c r="F20">
+      <c r="F20" t="s">
+        <v>110</v>
+      </c>
+      <c r="G20">
         <v>2</v>
       </c>
-      <c r="G20" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H20" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" t="s">
         <v>46</v>
       </c>
-      <c r="C21" t="s">
-        <v>47</v>
-      </c>
       <c r="D21" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E21" t="s">
-        <v>53</v>
-      </c>
-      <c r="F21">
+        <v>49</v>
+      </c>
+      <c r="G21">
         <v>2</v>
       </c>
-      <c r="G21" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H21" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C22" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E22" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+        <v>32</v>
+      </c>
+      <c r="F22" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C23" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D23" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E23" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+        <v>32</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C24" t="s">
+        <v>69</v>
+      </c>
+      <c r="D24" t="s">
+        <v>30</v>
+      </c>
+      <c r="E24" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B25" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C25" s="7"/>
+      <c r="E25" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s">
         <v>73</v>
       </c>
-      <c r="D24" t="s">
+      <c r="C26" t="s">
+        <v>92</v>
+      </c>
+      <c r="D26" t="s">
+        <v>63</v>
+      </c>
+      <c r="E26" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" t="s">
+        <v>93</v>
+      </c>
+      <c r="D27" t="s">
+        <v>63</v>
+      </c>
+      <c r="E27" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s">
+        <v>75</v>
+      </c>
+      <c r="C28" t="s">
+        <v>94</v>
+      </c>
+      <c r="D28" t="s">
+        <v>63</v>
+      </c>
+      <c r="E28" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29" t="s">
+        <v>76</v>
+      </c>
+      <c r="C29" t="s">
+        <v>95</v>
+      </c>
+      <c r="D29" t="s">
+        <v>63</v>
+      </c>
+      <c r="E29" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s">
+        <v>77</v>
+      </c>
+      <c r="C30" t="s">
+        <v>93</v>
+      </c>
+      <c r="D30" t="s">
+        <v>63</v>
+      </c>
+      <c r="E30" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31" t="s">
+        <v>78</v>
+      </c>
+      <c r="C31" t="s">
+        <v>96</v>
+      </c>
+      <c r="D31" t="s">
+        <v>63</v>
+      </c>
+      <c r="E31" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32" t="s">
+        <v>79</v>
+      </c>
+      <c r="C32" t="s">
+        <v>97</v>
+      </c>
+      <c r="D32" t="s">
+        <v>63</v>
+      </c>
+      <c r="E32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33">
         <v>31</v>
       </c>
-      <c r="E24" t="s">
+      <c r="B33" t="s">
+        <v>80</v>
+      </c>
+      <c r="C33" t="s">
+        <v>92</v>
+      </c>
+      <c r="D33" t="s">
+        <v>63</v>
+      </c>
+      <c r="E33" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B34" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C34" s="6"/>
+      <c r="E34" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>32</v>
+      </c>
+      <c r="B35" t="s">
+        <v>81</v>
+      </c>
+      <c r="C35" t="s">
+        <v>98</v>
+      </c>
+      <c r="D35" t="s">
+        <v>63</v>
+      </c>
+      <c r="E35" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36">
         <v>33</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A25">
-        <v>24</v>
-      </c>
-      <c r="B25" t="s">
-        <v>77</v>
-      </c>
-      <c r="C25" t="s">
-        <v>96</v>
-      </c>
-      <c r="D25" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26" t="s">
-        <v>78</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="B36" t="s">
+        <v>82</v>
+      </c>
+      <c r="C36" t="s">
+        <v>99</v>
+      </c>
+      <c r="D36" t="s">
+        <v>63</v>
+      </c>
+      <c r="E36" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>34</v>
+      </c>
+      <c r="B37" t="s">
+        <v>83</v>
+      </c>
+      <c r="C37" t="s">
+        <v>100</v>
+      </c>
+      <c r="D37" t="s">
+        <v>63</v>
+      </c>
+      <c r="E37" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>35</v>
+      </c>
+      <c r="B38" t="s">
+        <v>84</v>
+      </c>
+      <c r="C38" t="s">
         <v>97</v>
       </c>
-      <c r="D26" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A27">
-        <v>26</v>
-      </c>
-      <c r="B27" t="s">
-        <v>79</v>
-      </c>
-      <c r="C27" t="s">
-        <v>98</v>
-      </c>
-      <c r="D27" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28" t="s">
-        <v>80</v>
-      </c>
-      <c r="C28" t="s">
-        <v>99</v>
-      </c>
-      <c r="D28" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A29">
-        <v>28</v>
-      </c>
-      <c r="B29" t="s">
-        <v>81</v>
-      </c>
-      <c r="C29" t="s">
-        <v>97</v>
-      </c>
-      <c r="D29" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A30">
-        <v>29</v>
-      </c>
-      <c r="B30" t="s">
-        <v>82</v>
-      </c>
-      <c r="C30" t="s">
-        <v>100</v>
-      </c>
-      <c r="D30" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A31">
-        <v>30</v>
-      </c>
-      <c r="B31" t="s">
-        <v>83</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="D38" t="s">
+        <v>63</v>
+      </c>
+      <c r="E38" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>36</v>
+      </c>
+      <c r="B39" t="s">
+        <v>85</v>
+      </c>
+      <c r="C39" t="s">
+        <v>102</v>
+      </c>
+      <c r="D39" t="s">
+        <v>63</v>
+      </c>
+      <c r="E39" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>37</v>
+      </c>
+      <c r="B40" t="s">
+        <v>86</v>
+      </c>
+      <c r="C40" t="s">
+        <v>102</v>
+      </c>
+      <c r="D40" t="s">
+        <v>63</v>
+      </c>
+      <c r="E40" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B41" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C41" s="7"/>
+      <c r="E41" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>38</v>
+      </c>
+      <c r="B42" t="s">
+        <v>87</v>
+      </c>
+      <c r="C42" t="s">
         <v>101</v>
       </c>
-      <c r="D31" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A32">
-        <v>31</v>
-      </c>
-      <c r="B32" t="s">
-        <v>84</v>
-      </c>
-      <c r="C32" t="s">
-        <v>96</v>
-      </c>
-      <c r="D32" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33">
-        <v>32</v>
-      </c>
-      <c r="B33" t="s">
-        <v>85</v>
-      </c>
-      <c r="C33" t="s">
-        <v>102</v>
-      </c>
-      <c r="D33" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34">
+      <c r="D42" t="s">
+        <v>63</v>
+      </c>
+      <c r="E42" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>39</v>
+      </c>
+      <c r="B43" t="s">
+        <v>88</v>
+      </c>
+      <c r="C43" t="s">
+        <v>103</v>
+      </c>
+      <c r="D43" t="s">
+        <v>63</v>
+      </c>
+      <c r="E43" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>40</v>
+      </c>
+      <c r="B44" t="s">
+        <v>89</v>
+      </c>
+      <c r="C44" t="s">
+        <v>104</v>
+      </c>
+      <c r="D44" t="s">
+        <v>63</v>
+      </c>
+      <c r="E44" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>41</v>
+      </c>
+      <c r="B45" t="s">
+        <v>90</v>
+      </c>
+      <c r="C45" t="s">
+        <v>105</v>
+      </c>
+      <c r="D45" t="s">
+        <v>63</v>
+      </c>
+      <c r="E45" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B46" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C46" s="7"/>
+      <c r="E46" t="s">
         <v>33</v>
       </c>
-      <c r="B34" t="s">
-        <v>86</v>
-      </c>
-      <c r="C34" t="s">
-        <v>103</v>
-      </c>
-      <c r="D34" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35">
-        <v>34</v>
-      </c>
-      <c r="B35" t="s">
-        <v>87</v>
-      </c>
-      <c r="C35" t="s">
-        <v>104</v>
-      </c>
-      <c r="D35" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36">
-        <v>35</v>
-      </c>
-      <c r="B36" t="s">
-        <v>88</v>
-      </c>
-      <c r="C36" t="s">
-        <v>101</v>
-      </c>
-      <c r="D36" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37">
-        <v>36</v>
-      </c>
-      <c r="B37" t="s">
-        <v>89</v>
-      </c>
-      <c r="C37" t="s">
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>42</v>
+      </c>
+      <c r="B47" t="s">
+        <v>91</v>
+      </c>
+      <c r="C47" t="s">
         <v>106</v>
       </c>
-      <c r="D37" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38">
-        <v>37</v>
-      </c>
-      <c r="B38" t="s">
-        <v>90</v>
-      </c>
-      <c r="C38" t="s">
-        <v>106</v>
-      </c>
-      <c r="D38" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39">
-        <v>38</v>
-      </c>
-      <c r="B39" t="s">
-        <v>91</v>
-      </c>
-      <c r="C39" t="s">
-        <v>105</v>
-      </c>
-      <c r="D39" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40" t="s">
-        <v>92</v>
-      </c>
-      <c r="C40" t="s">
+      <c r="D47" t="s">
+        <v>63</v>
+      </c>
+      <c r="E47" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>43</v>
+      </c>
+      <c r="B48" t="s">
         <v>107</v>
       </c>
-      <c r="D40" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41" t="s">
-        <v>93</v>
-      </c>
-      <c r="C41" t="s">
+      <c r="C48" t="s">
         <v>108</v>
       </c>
-      <c r="D41" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42" t="s">
-        <v>94</v>
-      </c>
-      <c r="C42" t="s">
-        <v>109</v>
-      </c>
-      <c r="D42" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43" t="s">
-        <v>95</v>
-      </c>
-      <c r="C43" t="s">
-        <v>110</v>
-      </c>
-      <c r="D43" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A51">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A52">
+      <c r="D48" t="s">
+        <v>63</v>
+      </c>
+      <c r="E48" t="s">
         <v>33</v>
-      </c>
-      <c r="B52" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A53">
-        <v>34</v>
-      </c>
-      <c r="B53" t="s">
-        <v>49</v>
-      </c>
-      <c r="C53" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A54">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A55">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A56">
-        <v>37</v>
-      </c>
-      <c r="B56" t="s">
-        <v>51</v>
-      </c>
-      <c r="C56" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A57">
-        <v>38</v>
-      </c>
-      <c r="B57" t="s">
-        <v>52</v>
-      </c>
-      <c r="C57" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58">
-        <v>39</v>
-      </c>
-      <c r="B58" t="s">
-        <v>55</v>
-      </c>
-      <c r="C58" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>37</v>
+      </c>
+      <c r="B60" t="s">
+        <v>47</v>
+      </c>
+      <c r="C60" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>38</v>
+      </c>
+      <c r="B61" t="s">
+        <v>48</v>
+      </c>
+      <c r="C61" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>39</v>
+      </c>
+      <c r="B62" t="s">
+        <v>51</v>
+      </c>
+      <c r="C62" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A63">
         <v>40</v>
       </c>
-      <c r="B59" t="s">
-        <v>54</v>
-      </c>
-      <c r="C59" t="s">
-        <v>42</v>
+      <c r="B63" t="s">
+        <v>50</v>
+      </c>
+      <c r="C63" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1:D1048576">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+      <formula>"Not started"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
+      <formula>"In progress"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="11" priority="3" operator="equal">
+      <formula>"Done"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E1:F1048576">
+    <cfRule type="containsText" dxfId="10" priority="4" operator="containsText" text="Oskar">
+      <formula>NOT(ISERROR(SEARCH("Oskar",E1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="9" priority="5" operator="containsText" text="Hannah">
+      <formula>NOT(ISERROR(SEARCH("Hannah",E1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="8" priority="6" operator="containsText" text="Oliver">
+      <formula>NOT(ISERROR(SEARCH("Oliver",E1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="Thomas">
+      <formula>NOT(ISERROR(SEARCH("Thomas",E1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5873F9F0-B7E6-4151-BE75-8AB4F679080B}">
+  <dimension ref="A1:G30"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.54296875" style="8"/>
+    <col min="2" max="2" width="37.08984375" style="8" customWidth="1"/>
+    <col min="3" max="3" width="35.54296875" style="9" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" style="8"/>
+    <col min="5" max="5" width="15.1796875" style="8" customWidth="1"/>
+    <col min="6" max="6" width="11.54296875" style="8"/>
+    <col min="7" max="7" width="23.1796875" style="8" customWidth="1"/>
+    <col min="8" max="16384" width="11.54296875" style="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="8" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="8">
+        <v>1</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="F3" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A4" s="8">
+        <v>2</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="F4" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="8">
+        <v>3</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="F5" s="8">
+        <v>1</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="8">
+        <v>4</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="F6" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A7" s="8">
+        <v>5</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="F7" s="8">
+        <v>3</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="8">
+        <v>6</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="F8" s="8">
+        <v>2</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="8">
+        <v>7</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="F9" s="8">
+        <v>1</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="8">
+        <v>8</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="8">
+        <v>3</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="8">
+        <v>9</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" s="8">
+        <v>2</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="8">
+        <v>10</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" s="8">
+        <v>2</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A13" s="8">
+        <v>11</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="F13" s="8">
+        <v>2</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A14" s="8">
+        <v>12</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F14" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A15" s="8">
+        <v>13</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" s="8">
+        <v>14</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="F16" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" s="8">
+        <v>15</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="F17" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B18" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="F18" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="29.5" x14ac:dyDescent="0.4">
+      <c r="B19" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="F19" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22" s="8" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A23" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A24" s="8">
+        <v>1</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F24" s="8">
+        <v>2</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A25" s="8">
+        <v>2</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F25" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A26" s="8">
+        <v>3</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F26" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A27" s="8">
+        <v>4</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F27" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A28" s="8">
+        <v>5</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A29" s="8">
+        <v>6</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F29" s="8">
+        <v>2</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A30" s="8">
+        <v>7</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F30" s="8">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D2 D23">
     <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
-      <formula>"Not started"</formula>
+      <formula>$D$3</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
       <formula>"In progress"</formula>
@@ -1745,20 +2795,25 @@
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E1:E1048576">
+  <conditionalFormatting sqref="E2 E23">
     <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Oskar">
-      <formula>NOT(ISERROR(SEARCH("Oskar",E1)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Oskar",E2)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="Hannah">
-      <formula>NOT(ISERROR(SEARCH("Hannah",E1)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Hannah",E2)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="1" priority="6" operator="containsText" text="Oliver">
-      <formula>NOT(ISERROR(SEARCH("Oliver",E1)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Oliver",E2)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="0" priority="7" operator="containsText" text="Thomas">
-      <formula>NOT(ISERROR(SEARCH("Thomas",E1)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Thomas",E2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0249999999999999" bottom="1.0249999999999999" header="0.78749999999999998" footer="0.78749999999999998"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Arial,Regular"&amp;10&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Arial,Regular"&amp;10&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
--- a/Verbesserungsliste.xlsx
+++ b/Verbesserungsliste.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\neume\Desktop\MCI\Robotik_Projekt\Optimierung-Laboraufgabe-Robotik\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61480ECB-F542-41A5-BB0F-119DD967C47A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4585D820-14B2-4F96-997E-2B9901156268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22290" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="178">
   <si>
     <t>Nr.</t>
   </si>
@@ -350,24 +350,9 @@
     <t>Am Roboter</t>
   </si>
   <si>
-    <t>Zeitaufwand</t>
-  </si>
-  <si>
-    <t>2h</t>
-  </si>
-  <si>
     <t>NPN-LED durch größere PNP-LED ersetzen, Loch bohren</t>
   </si>
   <si>
-    <t>1h</t>
-  </si>
-  <si>
-    <t>3,5h</t>
-  </si>
-  <si>
-    <t>1,5h</t>
-  </si>
-  <si>
     <t>COGNEX-Anleitung</t>
   </si>
   <si>
@@ -564,6 +549,12 @@
   </si>
   <si>
     <t xml:space="preserve">Offen lassen </t>
+  </si>
+  <si>
+    <t>Verbesserung erster Roboter</t>
+  </si>
+  <si>
+    <t>x</t>
   </si>
 </sst>
 </file>
@@ -708,7 +699,37 @@
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
     <cellStyle name="Standard 2" xfId="1" xr:uid="{C5473660-9688-436F-8071-2AEA31843F41}"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="19">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <sz val="11"/>
@@ -829,34 +850,24 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor theme="0" tint="-0.34998626667073579"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -877,12 +888,6 @@
       </font>
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -897,18 +902,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{ADF0C628-87B5-4E6D-A20A-A83A20831158}" name="Tabelle1" displayName="Tabelle1" ref="A1:J48" totalsRowShown="0" headerRowDxfId="14">
-  <autoFilter ref="A1:J48" xr:uid="{ADF0C628-87B5-4E6D-A20A-A83A20831158}"/>
-  <tableColumns count="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{ADF0C628-87B5-4E6D-A20A-A83A20831158}" name="Tabelle1" displayName="Tabelle1" ref="A1:I73" totalsRowShown="0" headerRowDxfId="18">
+  <autoFilter ref="A1:I73" xr:uid="{ADF0C628-87B5-4E6D-A20A-A83A20831158}"/>
+  <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{05561CB3-D66F-4B3A-834B-EF02D87D9FD6}" name="Nr."/>
     <tableColumn id="2" xr3:uid="{F7DCFBA3-13FF-4C7B-8BF5-F13C6266F0A2}" name="Thema"/>
     <tableColumn id="3" xr3:uid="{574A6884-6A4F-4958-B5B5-BA2D1F8387B2}" name="Beschreibung"/>
     <tableColumn id="4" xr3:uid="{1E048EE8-98F7-43F9-9AC7-731BBEA2137B}" name="Status"/>
     <tableColumn id="5" xr3:uid="{FA5A1335-E3E8-486B-83D1-5FF8ADEE52FA}" name="Verantwortlicher"/>
-    <tableColumn id="6" xr3:uid="{58BEAA5F-C6AD-4B13-BF34-4D565CC30F12}" name="Zeitaufwand"/>
     <tableColumn id="7" xr3:uid="{B1B773FB-CBCD-4944-824A-E682569C730B}" name="Priorität"/>
-    <tableColumn id="8" xr3:uid="{1A2614E9-A6B9-421C-B8C6-2E52C63CD053}" name="Pflicht" dataDxfId="16"/>
-    <tableColumn id="9" xr3:uid="{F8040B49-6F6B-472D-BBAE-CD038BF42272}" name="Nice to have" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{1A2614E9-A6B9-421C-B8C6-2E52C63CD053}" name="Pflicht" dataDxfId="17"/>
+    <tableColumn id="9" xr3:uid="{F8040B49-6F6B-472D-BBAE-CD038BF42272}" name="Nice to have" dataDxfId="16"/>
     <tableColumn id="10" xr3:uid="{3C27D6E3-F773-4132-81C4-6F24859D6E70}" name="Benjamins Kommentare"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1202,21 +1206,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J63"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.1796875" customWidth="1"/>
     <col min="2" max="2" width="62.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="60.1796875" customWidth="1"/>
     <col min="4" max="4" width="10.54296875" customWidth="1"/>
-    <col min="5" max="6" width="19.26953125" customWidth="1"/>
-    <col min="7" max="7" width="9.81640625" customWidth="1"/>
-    <col min="8" max="8" width="9.1796875" style="5"/>
-    <col min="9" max="9" width="13.1796875" style="5" customWidth="1"/>
-    <col min="10" max="10" width="26.81640625" customWidth="1"/>
+    <col min="5" max="5" width="19.26953125" customWidth="1"/>
+    <col min="6" max="6" width="9.81640625" customWidth="1"/>
+    <col min="7" max="7" width="9.1796875" style="5"/>
+    <col min="8" max="8" width="13.1796875" style="5" customWidth="1"/>
+    <col min="9" max="9" width="70.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1233,22 +1237,19 @@
         <v>52</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="G1" s="3" t="s">
         <v>57</v>
       </c>
+      <c r="G1" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="H1" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1256,7 +1257,7 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D2" t="s">
         <v>30</v>
@@ -1264,17 +1265,14 @@
       <c r="E2" t="s">
         <v>32</v>
       </c>
-      <c r="F2" t="s">
-        <v>112</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2" s="5" t="s">
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1290,14 +1288,14 @@
       <c r="E3" t="s">
         <v>33</v>
       </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3" s="5" t="s">
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1313,20 +1311,17 @@
       <c r="E4" t="s">
         <v>32</v>
       </c>
-      <c r="F4" t="s">
-        <v>110</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-      <c r="H4" s="5" t="s">
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="J4" t="s">
+      <c r="I4" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1342,17 +1337,17 @@
       <c r="E5" t="s">
         <v>41</v>
       </c>
-      <c r="G5">
+      <c r="F5">
         <v>3</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="H5" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="J5" t="s">
+      <c r="I5" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1368,20 +1363,17 @@
       <c r="E6" t="s">
         <v>32</v>
       </c>
-      <c r="F6" t="s">
-        <v>113</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-      <c r="H6" s="5" t="s">
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="J6" t="s">
+      <c r="I6" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1397,17 +1389,17 @@
       <c r="E7" t="s">
         <v>49</v>
       </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7" s="5" t="s">
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="J7" t="s">
+      <c r="I7" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1423,14 +1415,14 @@
       <c r="E8" t="s">
         <v>33</v>
       </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8" s="5" t="s">
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1446,17 +1438,17 @@
       <c r="E9" t="s">
         <v>49</v>
       </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-      <c r="H9" s="5" t="s">
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="J9" t="s">
+      <c r="I9" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1472,17 +1464,14 @@
       <c r="E10" t="s">
         <v>32</v>
       </c>
-      <c r="F10" t="s">
-        <v>114</v>
-      </c>
-      <c r="G10">
+      <c r="F10">
         <v>3</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="H10" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1498,14 +1487,14 @@
       <c r="E11" t="s">
         <v>33</v>
       </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11" s="5" t="s">
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1522,16 +1511,13 @@
         <v>32</v>
       </c>
       <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>2</v>
-      </c>
-      <c r="H12" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="G12" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1547,20 +1533,17 @@
       <c r="E13" t="s">
         <v>32</v>
       </c>
-      <c r="F13" t="s">
-        <v>110</v>
-      </c>
-      <c r="G13">
-        <v>2</v>
-      </c>
-      <c r="H13" s="5" t="s">
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="J13" t="s">
+      <c r="I13" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1576,14 +1559,14 @@
       <c r="E14" t="s">
         <v>41</v>
       </c>
-      <c r="G14">
-        <v>2</v>
-      </c>
-      <c r="H14" s="5" t="s">
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1599,17 +1582,17 @@
       <c r="E15" t="s">
         <v>41</v>
       </c>
-      <c r="G15">
-        <v>2</v>
-      </c>
-      <c r="H15" s="5" t="s">
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="J15" t="s">
+      <c r="I15" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1625,14 +1608,14 @@
       <c r="E16" t="s">
         <v>41</v>
       </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-      <c r="H16" s="5" t="s">
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1648,14 +1631,14 @@
       <c r="E17" t="s">
         <v>41</v>
       </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-      <c r="H17" s="5" t="s">
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1671,14 +1654,14 @@
       <c r="E18" t="s">
         <v>33</v>
       </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-      <c r="H18" s="5" t="s">
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1694,17 +1677,17 @@
       <c r="E19" t="s">
         <v>49</v>
       </c>
-      <c r="G19">
+      <c r="F19">
         <v>3</v>
       </c>
-      <c r="I19" s="5" t="s">
+      <c r="H19" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="J19" t="s">
+      <c r="I19" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1720,17 +1703,14 @@
       <c r="E20" t="s">
         <v>32</v>
       </c>
-      <c r="F20" t="s">
-        <v>110</v>
-      </c>
-      <c r="G20">
-        <v>2</v>
-      </c>
-      <c r="H20" s="5" t="s">
+      <c r="F20">
+        <v>2</v>
+      </c>
+      <c r="G20" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1746,14 +1726,14 @@
       <c r="E21" t="s">
         <v>49</v>
       </c>
-      <c r="G21">
-        <v>2</v>
-      </c>
-      <c r="H21" s="5" t="s">
+      <c r="F21">
+        <v>2</v>
+      </c>
+      <c r="G21" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1769,11 +1749,14 @@
       <c r="E22" t="s">
         <v>32</v>
       </c>
-      <c r="F22" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1790,10 +1773,13 @@
         <v>32</v>
       </c>
       <c r="F23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1809,20 +1795,29 @@
       <c r="E24" t="s">
         <v>32</v>
       </c>
-      <c r="F24" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="F24">
+        <v>3</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B25" s="7" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C25" s="7"/>
+      <c r="D25" t="s">
+        <v>63</v>
+      </c>
       <c r="E25" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="F25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>24</v>
       </c>
@@ -1838,8 +1833,14 @@
       <c r="E26" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="F26">
+        <v>2</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>25</v>
       </c>
@@ -1855,8 +1856,14 @@
       <c r="E27" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="F27">
+        <v>3</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>26</v>
       </c>
@@ -1872,8 +1879,14 @@
       <c r="E28" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>27</v>
       </c>
@@ -1889,8 +1902,14 @@
       <c r="E29" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>28</v>
       </c>
@@ -1906,8 +1925,14 @@
       <c r="E30" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>29</v>
       </c>
@@ -1923,8 +1948,14 @@
       <c r="E31" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>30</v>
       </c>
@@ -1940,8 +1971,14 @@
       <c r="E32" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>31</v>
       </c>
@@ -1957,17 +1994,32 @@
       <c r="E33" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F33">
+        <v>3</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B34" s="7" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C34" s="6"/>
+      <c r="D34" t="s">
+        <v>63</v>
+      </c>
       <c r="E34" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>32</v>
       </c>
@@ -1983,8 +2035,14 @@
       <c r="E35" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>33</v>
       </c>
@@ -2000,8 +2058,14 @@
       <c r="E36" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F36">
+        <v>1</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>34</v>
       </c>
@@ -2017,8 +2081,14 @@
       <c r="E37" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F37">
+        <v>1</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>35</v>
       </c>
@@ -2034,8 +2104,14 @@
       <c r="E38" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F38">
+        <v>2</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>36</v>
       </c>
@@ -2051,8 +2127,14 @@
       <c r="E39" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F39">
+        <v>2</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>37</v>
       </c>
@@ -2068,17 +2150,32 @@
       <c r="E40" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F40">
+        <v>2</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B41" s="7" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C41" s="7"/>
+      <c r="D41" t="s">
+        <v>63</v>
+      </c>
       <c r="E41" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F41">
+        <v>2</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>38</v>
       </c>
@@ -2094,8 +2191,14 @@
       <c r="E42" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F42">
+        <v>2</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>39</v>
       </c>
@@ -2111,8 +2214,14 @@
       <c r="E43" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F43">
+        <v>2</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>40</v>
       </c>
@@ -2128,8 +2237,14 @@
       <c r="E44" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F44">
+        <v>2</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>41</v>
       </c>
@@ -2145,19 +2260,37 @@
       <c r="E45" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F45">
+        <v>2</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>42</v>
+      </c>
       <c r="B46" s="7" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C46" s="7"/>
+      <c r="D46" t="s">
+        <v>31</v>
+      </c>
       <c r="E46" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F46">
+        <v>1</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B47" t="s">
         <v>91</v>
@@ -2171,10 +2304,16 @@
       <c r="E47" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F47">
+        <v>1</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B48" t="s">
         <v>107</v>
@@ -2188,85 +2327,678 @@
       <c r="E48" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="F48">
+        <v>2</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>45</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F49" s="8">
+        <v>1</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>46</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="D50" t="s">
+        <v>63</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F50" s="8">
+        <v>1</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>47</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="D51" t="s">
+        <v>63</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F51" s="8">
+        <v>1</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="I51" s="8" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>48</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="D52" t="s">
+        <v>63</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F52" s="8">
+        <v>1</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="I52" s="8"/>
+    </row>
+    <row r="53" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>49</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="D53" t="s">
+        <v>63</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="F53" s="8">
+        <v>3</v>
+      </c>
+      <c r="H53" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="I53" s="8" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>50</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="D54" t="s">
+        <v>63</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="F54" s="8">
+        <v>2</v>
+      </c>
+      <c r="H54" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="I54" s="8" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>51</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="D55" t="s">
+        <v>63</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F55" s="8">
+        <v>1</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="I55" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>52</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="D56" t="s">
+        <v>63</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F56" s="8">
+        <v>3</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="I56" s="8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>53</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="D57" t="s">
+        <v>63</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F57" s="8">
+        <v>2</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="I57" s="8" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+        <v>54</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D58" t="s">
+        <v>63</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F58" s="8">
+        <v>2</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="I58" s="8" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="D59" t="s">
+        <v>63</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F59" s="8">
+        <v>2</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="I59" s="8" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60">
-        <v>37</v>
-      </c>
-      <c r="B60" t="s">
+        <v>56</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="D60" t="s">
+        <v>63</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F60" s="8">
+        <v>3</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>57</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="D61" t="s">
+        <v>63</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F61" s="8">
+        <v>2</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>58</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="D62" t="s">
+        <v>63</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="F62" s="8">
+        <v>1</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>59</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C63" s="9"/>
+      <c r="D63" t="s">
+        <v>63</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="F63" s="8">
+        <v>3</v>
+      </c>
+      <c r="H63" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>60</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="C64" s="9"/>
+      <c r="D64" t="s">
+        <v>63</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="F64" s="8">
+        <v>1</v>
+      </c>
+      <c r="G64" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="17" x14ac:dyDescent="0.4">
+      <c r="A65">
+        <v>61</v>
+      </c>
+      <c r="B65" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="D65" t="s">
+        <v>31</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="F65" s="8">
+        <v>1</v>
+      </c>
+      <c r="G65" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>62</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="D66" t="s">
+        <v>63</v>
+      </c>
+      <c r="E66" t="s">
+        <v>170</v>
+      </c>
+      <c r="F66">
+        <v>2</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>63</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="D67" t="s">
+        <v>63</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F67" s="8">
+        <v>2</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="I67" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>64</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="D68" t="s">
+        <v>63</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F68" s="8">
+        <v>2</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="I68" s="8"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <v>65</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="D69" t="s">
+        <v>63</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F69" s="8">
+        <v>2</v>
+      </c>
+      <c r="G69" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="I69" s="8"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <v>66</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="D70" t="s">
+        <v>63</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F70" s="8">
+        <v>3</v>
+      </c>
+      <c r="G70" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="I70" s="8"/>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A71">
+        <v>67</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="D71" t="s">
+        <v>63</v>
+      </c>
+      <c r="E71" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="F71" s="8"/>
+      <c r="H71" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="I71" s="8" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A72">
+        <v>68</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C72" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D72" t="s">
+        <v>63</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="F72" s="8">
+        <v>2</v>
+      </c>
+      <c r="H72" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="I72" s="8" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A73">
+        <v>69</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C73" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D73" t="s">
+        <v>63</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F73" s="8">
+        <v>2</v>
+      </c>
+      <c r="G73" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B77" t="s">
         <v>47</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C77" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A61">
-        <v>38</v>
-      </c>
-      <c r="B61" t="s">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B78" t="s">
         <v>48</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C78" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A62">
-        <v>39</v>
-      </c>
-      <c r="B62" t="s">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B79" t="s">
         <v>51</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C79" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A63">
-        <v>40</v>
-      </c>
-      <c r="B63" t="s">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B80" t="s">
         <v>50</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C80" t="s">
         <v>41</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+  <conditionalFormatting sqref="D2:D73">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"Not started"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
       <formula>"In progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E1:F1048576">
-    <cfRule type="containsText" dxfId="10" priority="4" operator="containsText" text="Oskar">
-      <formula>NOT(ISERROR(SEARCH("Oskar",E1)))</formula>
+  <conditionalFormatting sqref="E2:E73">
+    <cfRule type="containsText" dxfId="15" priority="1" operator="containsText" text="Alle">
+      <formula>NOT(ISERROR(SEARCH("Alle",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="5" operator="containsText" text="Hannah">
-      <formula>NOT(ISERROR(SEARCH("Hannah",E1)))</formula>
+    <cfRule type="containsText" dxfId="14" priority="2" operator="containsText" text="Offen lassen">
+      <formula>NOT(ISERROR(SEARCH("Offen lassen",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="6" operator="containsText" text="Oliver">
-      <formula>NOT(ISERROR(SEARCH("Oliver",E1)))</formula>
+    <cfRule type="containsText" dxfId="13" priority="6" operator="containsText" text="Oskar">
+      <formula>NOT(ISERROR(SEARCH("Oskar",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="Thomas">
-      <formula>NOT(ISERROR(SEARCH("Thomas",E1)))</formula>
+    <cfRule type="containsText" dxfId="12" priority="7" operator="containsText" text="Hannah">
+      <formula>NOT(ISERROR(SEARCH("Hannah",E2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="11" priority="8" operator="containsText" text="Oliver">
+      <formula>NOT(ISERROR(SEARCH("Oliver",E2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="10" priority="9" operator="containsText" text="Thomas">
+      <formula>NOT(ISERROR(SEARCH("Thomas",E2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2294,7 +3026,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
@@ -2325,16 +3057,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F3" s="8">
         <v>1</v>
@@ -2345,16 +3077,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>168</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>173</v>
       </c>
       <c r="F4" s="8">
         <v>1</v>
@@ -2365,22 +3097,22 @@
         <v>3</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F5" s="8">
         <v>1</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
@@ -2388,13 +3120,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F6" s="8">
         <v>1</v>
@@ -2405,19 +3137,19 @@
         <v>5</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="F7" s="8">
         <v>3</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
@@ -2425,19 +3157,19 @@
         <v>6</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="F8" s="8">
         <v>2</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
@@ -2445,19 +3177,19 @@
         <v>7</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F9" s="8">
         <v>1</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
@@ -2465,10 +3197,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>32</v>
@@ -2477,7 +3209,7 @@
         <v>3</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
@@ -2485,10 +3217,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>32</v>
@@ -2497,7 +3229,7 @@
         <v>2</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
@@ -2505,10 +3237,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>32</v>
@@ -2517,7 +3249,7 @@
         <v>2</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -2525,19 +3257,19 @@
         <v>11</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F13" s="8">
         <v>2</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -2545,10 +3277,10 @@
         <v>12</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>49</v>
@@ -2562,10 +3294,10 @@
         <v>13</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>41</v>
@@ -2579,13 +3311,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="F16" s="8">
         <v>1</v>
@@ -2596,10 +3328,10 @@
         <v>15</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="F17" s="8">
         <v>3</v>
@@ -2607,10 +3339,10 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B18" s="8" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="F18" s="8">
         <v>1</v>
@@ -2618,13 +3350,13 @@
     </row>
     <row r="19" spans="1:7" ht="29.5" x14ac:dyDescent="0.4">
       <c r="B19" s="14" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="F19" s="8">
         <v>1</v>
@@ -2632,7 +3364,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
@@ -2663,10 +3395,10 @@
         <v>1</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="E24" s="8" t="s">
         <v>49</v>
@@ -2675,7 +3407,7 @@
         <v>2</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
@@ -2683,10 +3415,10 @@
         <v>2</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="E25" s="8" t="s">
         <v>49</v>
@@ -2700,10 +3432,10 @@
         <v>3</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E26" s="8" t="s">
         <v>49</v>
@@ -2717,10 +3449,10 @@
         <v>4</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E27" s="8" t="s">
         <v>41</v>
@@ -2734,16 +3466,16 @@
         <v>5</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E28" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="G28" s="8" t="s">
         <v>174</v>
-      </c>
-      <c r="G28" s="8" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -2751,19 +3483,19 @@
         <v>6</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="F29" s="8">
         <v>2</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
@@ -2771,10 +3503,10 @@
         <v>7</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="E30" s="8" t="s">
         <v>32</v>
@@ -2785,27 +3517,27 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2 D23">
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
       <formula>$D$3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
       <formula>"In progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2 E23">
-    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Oskar">
+    <cfRule type="containsText" dxfId="6" priority="4" operator="containsText" text="Oskar">
       <formula>NOT(ISERROR(SEARCH("Oskar",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="Hannah">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="Hannah">
       <formula>NOT(ISERROR(SEARCH("Hannah",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="6" operator="containsText" text="Oliver">
+    <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="Oliver">
       <formula>NOT(ISERROR(SEARCH("Oliver",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="7" operator="containsText" text="Thomas">
+    <cfRule type="containsText" dxfId="3" priority="7" operator="containsText" text="Thomas">
       <formula>NOT(ISERROR(SEARCH("Thomas",E2)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Verbesserungsliste.xlsx
+++ b/Verbesserungsliste.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\neume\Desktop\MCI\Robotik_Projekt\Optimierung-Laboraufgabe-Robotik\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4585D820-14B2-4F96-997E-2B9901156268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D5ED2AD-DE70-4E00-91F8-12C81B8EC8AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="180">
   <si>
     <t>Nr.</t>
   </si>
@@ -555,6 +555,12 @@
   </si>
   <si>
     <t>x</t>
+  </si>
+  <si>
+    <t>Abdeckungen + LED zweiter Roboter</t>
+  </si>
+  <si>
+    <t>Abdeckungen + LED erster Roboter</t>
   </si>
 </sst>
 </file>
@@ -702,36 +708,6 @@
   <dxfs count="19">
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <sz val="11"/>
         <color rgb="FF000000"/>
         <name val="Calibri"/>
@@ -860,6 +836,36 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1207,20 +1213,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.1796875" customWidth="1"/>
-    <col min="2" max="2" width="62.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="60.1796875" customWidth="1"/>
-    <col min="4" max="4" width="10.54296875" customWidth="1"/>
-    <col min="5" max="5" width="19.26953125" customWidth="1"/>
-    <col min="6" max="6" width="9.81640625" customWidth="1"/>
-    <col min="7" max="7" width="9.1796875" style="5"/>
-    <col min="8" max="8" width="13.1796875" style="5" customWidth="1"/>
-    <col min="9" max="9" width="70.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.140625" customWidth="1"/>
+    <col min="2" max="2" width="62.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="60.140625" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="5"/>
+    <col min="8" max="8" width="13.140625" style="5" customWidth="1"/>
+    <col min="9" max="9" width="70.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1249,7 +1255,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1272,7 +1278,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1295,7 +1301,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1321,7 +1327,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1347,7 +1353,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1373,7 +1379,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1399,7 +1405,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1422,7 +1428,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1448,7 +1454,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1471,7 +1477,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1494,7 +1500,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1517,7 +1523,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1543,7 +1549,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1566,7 +1572,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1592,7 +1598,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1615,7 +1621,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1638,7 +1644,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1661,7 +1667,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1687,7 +1693,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1710,7 +1716,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1733,7 +1739,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1756,7 +1762,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1779,7 +1785,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1802,7 +1808,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B25" s="7" t="s">
         <v>110</v>
       </c>
@@ -1817,7 +1823,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>24</v>
       </c>
@@ -1840,7 +1846,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>25</v>
       </c>
@@ -1863,7 +1869,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26</v>
       </c>
@@ -1886,7 +1892,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>27</v>
       </c>
@@ -1909,7 +1915,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>28</v>
       </c>
@@ -1932,7 +1938,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>29</v>
       </c>
@@ -1955,7 +1961,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>30</v>
       </c>
@@ -1978,7 +1984,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>31</v>
       </c>
@@ -2001,7 +2007,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B34" s="7" t="s">
         <v>111</v>
       </c>
@@ -2019,7 +2025,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>32</v>
       </c>
@@ -2042,7 +2048,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>33</v>
       </c>
@@ -2065,7 +2071,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>34</v>
       </c>
@@ -2088,7 +2094,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>35</v>
       </c>
@@ -2111,7 +2117,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>36</v>
       </c>
@@ -2134,7 +2140,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>37</v>
       </c>
@@ -2157,7 +2163,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B41" s="7" t="s">
         <v>112</v>
       </c>
@@ -2175,7 +2181,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>38</v>
       </c>
@@ -2198,7 +2204,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>39</v>
       </c>
@@ -2221,7 +2227,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>40</v>
       </c>
@@ -2244,7 +2250,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>41</v>
       </c>
@@ -2267,7 +2273,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>42</v>
       </c>
@@ -2288,7 +2294,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>43</v>
       </c>
@@ -2311,7 +2317,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>44</v>
       </c>
@@ -2334,7 +2340,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>45</v>
       </c>
@@ -2357,7 +2363,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>46</v>
       </c>
@@ -2380,7 +2386,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>47</v>
       </c>
@@ -2406,7 +2412,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>48</v>
       </c>
@@ -2430,7 +2436,7 @@
       </c>
       <c r="I52" s="8"/>
     </row>
-    <row r="53" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>49</v>
       </c>
@@ -2456,7 +2462,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>50</v>
       </c>
@@ -2482,7 +2488,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>51</v>
       </c>
@@ -2508,7 +2514,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>52</v>
       </c>
@@ -2519,7 +2525,7 @@
         <v>146</v>
       </c>
       <c r="D56" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="E56" s="8" t="s">
         <v>32</v>
@@ -2534,7 +2540,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>53</v>
       </c>
@@ -2560,12 +2566,12 @@
         <v>142</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>54</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>115</v>
+        <v>178</v>
       </c>
       <c r="C58" s="9" t="s">
         <v>114</v>
@@ -2586,7 +2592,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>55</v>
       </c>
@@ -2612,7 +2618,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>56</v>
       </c>
@@ -2635,7 +2641,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>57</v>
       </c>
@@ -2658,7 +2664,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>58</v>
       </c>
@@ -2681,7 +2687,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>59</v>
       </c>
@@ -2702,7 +2708,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>60</v>
       </c>
@@ -2723,7 +2729,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="17" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>61</v>
       </c>
@@ -2746,7 +2752,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>62</v>
       </c>
@@ -2766,7 +2772,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>63</v>
       </c>
@@ -2792,7 +2798,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>64</v>
       </c>
@@ -2816,7 +2822,7 @@
       </c>
       <c r="I68" s="8"/>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>65</v>
       </c>
@@ -2830,7 +2836,7 @@
         <v>63</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="F69" s="8">
         <v>2</v>
@@ -2840,7 +2846,7 @@
       </c>
       <c r="I69" s="8"/>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>66</v>
       </c>
@@ -2864,7 +2870,7 @@
       </c>
       <c r="I70" s="8"/>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>67</v>
       </c>
@@ -2888,7 +2894,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>68</v>
       </c>
@@ -2914,18 +2920,18 @@
         <v>171</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>69</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>115</v>
+        <v>179</v>
       </c>
       <c r="C73" s="9" t="s">
         <v>114</v>
       </c>
       <c r="D73" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="E73" s="8" t="s">
         <v>32</v>
@@ -2937,7 +2943,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
         <v>47</v>
       </c>
@@ -2945,7 +2951,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
         <v>48</v>
       </c>
@@ -2953,7 +2959,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
         <v>51</v>
       </c>
@@ -2961,7 +2967,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
         <v>50</v>
       </c>
@@ -2971,33 +2977,33 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D73">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="3" operator="equal">
       <formula>"Not started"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="4" operator="equal">
       <formula>"In progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="5" operator="equal">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E73">
-    <cfRule type="containsText" dxfId="15" priority="1" operator="containsText" text="Alle">
+    <cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="Alle">
       <formula>NOT(ISERROR(SEARCH("Alle",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="2" operator="containsText" text="Offen lassen">
+    <cfRule type="containsText" dxfId="11" priority="2" operator="containsText" text="Offen lassen">
       <formula>NOT(ISERROR(SEARCH("Offen lassen",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="6" operator="containsText" text="Oskar">
+    <cfRule type="containsText" dxfId="10" priority="6" operator="containsText" text="Oskar">
       <formula>NOT(ISERROR(SEARCH("Oskar",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="7" operator="containsText" text="Hannah">
+    <cfRule type="containsText" dxfId="9" priority="7" operator="containsText" text="Hannah">
       <formula>NOT(ISERROR(SEARCH("Hannah",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="8" operator="containsText" text="Oliver">
+    <cfRule type="containsText" dxfId="8" priority="8" operator="containsText" text="Oliver">
       <formula>NOT(ISERROR(SEARCH("Oliver",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="9" operator="containsText" text="Thomas">
+    <cfRule type="containsText" dxfId="7" priority="9" operator="containsText" text="Thomas">
       <formula>NOT(ISERROR(SEARCH("Thomas",E2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3012,24 +3018,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5873F9F0-B7E6-4151-BE75-8AB4F679080B}">
   <dimension ref="A1:G30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.54296875" style="8"/>
-    <col min="2" max="2" width="37.08984375" style="8" customWidth="1"/>
-    <col min="3" max="3" width="35.54296875" style="9" customWidth="1"/>
-    <col min="4" max="4" width="11.54296875" style="8"/>
-    <col min="5" max="5" width="15.1796875" style="8" customWidth="1"/>
-    <col min="6" max="6" width="11.54296875" style="8"/>
-    <col min="7" max="7" width="23.1796875" style="8" customWidth="1"/>
-    <col min="8" max="16384" width="11.54296875" style="8"/>
+    <col min="1" max="1" width="11.5703125" style="8"/>
+    <col min="2" max="2" width="37.140625" style="8" customWidth="1"/>
+    <col min="3" max="3" width="35.5703125" style="9" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" style="8"/>
+    <col min="5" max="5" width="15.140625" style="8" customWidth="1"/>
+    <col min="6" max="6" width="11.5703125" style="8"/>
+    <col min="7" max="7" width="23.140625" style="8" customWidth="1"/>
+    <col min="8" max="16384" width="11.5703125" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>0</v>
       </c>
@@ -3052,7 +3058,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
         <v>1</v>
       </c>
@@ -3072,7 +3078,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
         <v>2</v>
       </c>
@@ -3092,7 +3098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
         <v>3</v>
       </c>
@@ -3115,7 +3121,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <v>4</v>
       </c>
@@ -3132,7 +3138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="8">
         <v>5</v>
       </c>
@@ -3152,7 +3158,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <v>6</v>
       </c>
@@ -3172,7 +3178,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
         <v>7</v>
       </c>
@@ -3192,7 +3198,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
         <v>8</v>
       </c>
@@ -3212,7 +3218,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
         <v>9</v>
       </c>
@@ -3232,7 +3238,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
         <v>10</v>
       </c>
@@ -3252,7 +3258,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
         <v>11</v>
       </c>
@@ -3272,7 +3278,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
         <v>12</v>
       </c>
@@ -3289,7 +3295,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
         <v>13</v>
       </c>
@@ -3306,7 +3312,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
         <v>14</v>
       </c>
@@ -3323,7 +3329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
         <v>15</v>
       </c>
@@ -3337,7 +3343,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B18" s="8" t="s">
         <v>130</v>
       </c>
@@ -3348,7 +3354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="29.5" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:7" ht="30.75" x14ac:dyDescent="0.3">
       <c r="B19" s="14" t="s">
         <v>129</v>
       </c>
@@ -3362,12 +3368,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
         <v>0</v>
       </c>
@@ -3390,7 +3396,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
         <v>1</v>
       </c>
@@ -3410,7 +3416,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="8">
         <v>2</v>
       </c>
@@ -3427,7 +3433,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="8">
         <v>3</v>
       </c>
@@ -3444,7 +3450,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="8">
         <v>4</v>
       </c>
@@ -3461,7 +3467,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="8">
         <v>5</v>
       </c>
@@ -3478,7 +3484,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="8">
         <v>6</v>
       </c>
@@ -3498,7 +3504,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="8">
         <v>7</v>
       </c>
@@ -3517,27 +3523,27 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2 D23">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
       <formula>$D$3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
       <formula>"In progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2 E23">
-    <cfRule type="containsText" dxfId="6" priority="4" operator="containsText" text="Oskar">
+    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Oskar">
       <formula>NOT(ISERROR(SEARCH("Oskar",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="Hannah">
+    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="Hannah">
       <formula>NOT(ISERROR(SEARCH("Hannah",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="Oliver">
+    <cfRule type="containsText" dxfId="1" priority="6" operator="containsText" text="Oliver">
       <formula>NOT(ISERROR(SEARCH("Oliver",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="7" operator="containsText" text="Thomas">
+    <cfRule type="containsText" dxfId="0" priority="7" operator="containsText" text="Thomas">
       <formula>NOT(ISERROR(SEARCH("Thomas",E2)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Verbesserungsliste.xlsx
+++ b/Verbesserungsliste.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\neume\Desktop\MCI\Robotik_Projekt\Optimierung-Laboraufgabe-Robotik\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D5ED2AD-DE70-4E00-91F8-12C81B8EC8AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B53C793B-B68C-44D4-9500-5D1F750015C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="ToDos" sheetId="1" r:id="rId1"/>
+    <sheet name="Notes" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="188">
   <si>
     <t>Nr.</t>
   </si>
@@ -143,9 +143,6 @@
     <t>drei getrennte Kabel, Beschriftung, Anleitung</t>
   </si>
   <si>
-    <t>Angebote einholen für das Gegenstück aus Alu (Xometry), erst testen mit 3D-Druck</t>
-  </si>
-  <si>
     <t>Hannah</t>
   </si>
   <si>
@@ -182,9 +179,6 @@
     <t>Verantwortlicher</t>
   </si>
   <si>
-    <t>geschraubt</t>
-  </si>
-  <si>
     <t>Plexiglas mit Nieten</t>
   </si>
   <si>
@@ -561,13 +555,43 @@
   </si>
   <si>
     <t>Abdeckungen + LED erster Roboter</t>
+  </si>
+  <si>
+    <t>Check nochmal Ende Februar durchführen</t>
+  </si>
+  <si>
+    <t>Misumi für TCP-Spitze, lange Alu-Spitze verwerfen (wird ersetzt durch TeachingSpitze)</t>
+  </si>
+  <si>
+    <t>wurde neu gedruckt</t>
+  </si>
+  <si>
+    <t>Schranke wurde im neuem Kameraturm nach vorne geschoben</t>
+  </si>
+  <si>
+    <t>Gedruckt (Test noch ausstehend)</t>
+  </si>
+  <si>
+    <t>Adapter wird nicht mehr benötigt (Schnellwechsler im Einsatz)</t>
+  </si>
+  <si>
+    <t>Bereits für beide Anlagen umgesetzt</t>
+  </si>
+  <si>
+    <t>Wurde gedruckt (Qualtitä sehr schlecht --&gt; 3D nochmal anpassen)</t>
+  </si>
+  <si>
+    <t>Wird direkt in die neue Abdeckung eingebaut</t>
+  </si>
+  <si>
+    <t>Kommentare</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -602,6 +626,13 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -660,7 +691,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -700,6 +731,7 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -919,7 +951,7 @@
     <tableColumn id="7" xr3:uid="{B1B773FB-CBCD-4944-824A-E682569C730B}" name="Priorität"/>
     <tableColumn id="8" xr3:uid="{1A2614E9-A6B9-421C-B8C6-2E52C63CD053}" name="Pflicht" dataDxfId="17"/>
     <tableColumn id="9" xr3:uid="{F8040B49-6F6B-472D-BBAE-CD038BF42272}" name="Nice to have" dataDxfId="16"/>
-    <tableColumn id="10" xr3:uid="{3C27D6E3-F773-4132-81C4-6F24859D6E70}" name="Benjamins Kommentare"/>
+    <tableColumn id="10" xr3:uid="{3C27D6E3-F773-4132-81C4-6F24859D6E70}" name="Kommentare"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1212,18 +1244,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.140625" customWidth="1"/>
     <col min="2" max="2" width="62.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="60.140625" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.28515625" customWidth="1"/>
     <col min="6" max="6" width="9.85546875" customWidth="1"/>
     <col min="7" max="7" width="9.140625" style="5"/>
     <col min="8" max="8" width="13.140625" style="5" customWidth="1"/>
-    <col min="9" max="9" width="70.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="81" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1240,10 +1275,10 @@
         <v>28</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>35</v>
@@ -1252,7 +1287,7 @@
         <v>36</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>59</v>
+        <v>187</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -1263,7 +1298,7 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D2" t="s">
         <v>30</v>
@@ -1276,6 +1311,9 @@
       </c>
       <c r="G2" s="5" t="s">
         <v>29</v>
+      </c>
+      <c r="I2" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -1324,7 +1362,7 @@
         <v>29</v>
       </c>
       <c r="I4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -1332,16 +1370,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F5">
         <v>3</v>
@@ -1350,7 +1388,7 @@
         <v>29</v>
       </c>
       <c r="I5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -1361,7 +1399,7 @@
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D6" t="s">
         <v>30</v>
@@ -1376,7 +1414,7 @@
         <v>29</v>
       </c>
       <c r="I6" t="s">
-        <v>53</v>
+        <v>185</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -1393,7 +1431,7 @@
         <v>30</v>
       </c>
       <c r="E7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -1442,7 +1480,7 @@
         <v>31</v>
       </c>
       <c r="E9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F9">
         <v>2</v>
@@ -1462,7 +1500,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D10" t="s">
         <v>30</v>
@@ -1475,6 +1513,9 @@
       </c>
       <c r="H10" s="5" t="s">
         <v>29</v>
+      </c>
+      <c r="I10" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -1522,6 +1563,9 @@
       <c r="G12" s="5" t="s">
         <v>29</v>
       </c>
+      <c r="I12" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13">
@@ -1545,9 +1589,6 @@
       <c r="G13" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="I13" t="s">
-        <v>40</v>
-      </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14">
@@ -1563,7 +1604,7 @@
         <v>30</v>
       </c>
       <c r="E14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F14">
         <v>2</v>
@@ -1586,7 +1627,7 @@
         <v>30</v>
       </c>
       <c r="E15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F15">
         <v>2</v>
@@ -1595,7 +1636,7 @@
         <v>29</v>
       </c>
       <c r="I15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -1603,16 +1644,16 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" t="s">
         <v>70</v>
-      </c>
-      <c r="C16" t="s">
-        <v>72</v>
       </c>
       <c r="D16" t="s">
         <v>31</v>
       </c>
       <c r="E16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -1626,16 +1667,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C17" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D17" t="s">
         <v>30</v>
       </c>
       <c r="E17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -1681,7 +1722,7 @@
         <v>31</v>
       </c>
       <c r="E19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F19">
         <v>3</v>
@@ -1690,7 +1731,7 @@
         <v>29</v>
       </c>
       <c r="I19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -1698,10 +1739,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D20" t="s">
         <v>31</v>
@@ -1714,6 +1755,9 @@
       </c>
       <c r="G20" s="5" t="s">
         <v>29</v>
+      </c>
+      <c r="I20" s="15" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -1721,16 +1765,16 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" t="s">
         <v>45</v>
       </c>
-      <c r="C21" t="s">
-        <v>46</v>
-      </c>
       <c r="D21" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F21">
         <v>2</v>
@@ -1744,10 +1788,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C22" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D22" t="s">
         <v>30</v>
@@ -1759,7 +1803,10 @@
         <v>1</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
+      </c>
+      <c r="I22" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -1767,13 +1814,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C23" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D23" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E23" t="s">
         <v>32</v>
@@ -1782,7 +1829,7 @@
         <v>1</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -1790,10 +1837,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C24" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D24" t="s">
         <v>30</v>
@@ -1805,19 +1852,22 @@
         <v>3</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
+      </c>
+      <c r="I24" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B25" s="7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C25" s="7"/>
       <c r="D25" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F25">
         <v>2</v>
@@ -1828,22 +1878,22 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C26" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D26" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E26" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F26">
         <v>2</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -1851,22 +1901,22 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C27" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D27" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E27" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F27">
         <v>3</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -1874,22 +1924,22 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C28" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D28" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F28">
         <v>1</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -1897,22 +1947,22 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D29" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E29" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F29">
         <v>1</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -1920,22 +1970,22 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C30" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D30" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E30" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F30">
         <v>1</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -1943,22 +1993,22 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C31" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D31" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E31" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F31">
         <v>1</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -1966,22 +2016,22 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C32" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D32" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F32">
         <v>1</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -1989,40 +2039,40 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C33" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D33" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E33" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F33">
         <v>3</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B34" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E34" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F34">
         <v>1</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -2030,22 +2080,22 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C35" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D35" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E35" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F35">
         <v>1</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -2053,22 +2103,22 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C36" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D36" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E36" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F36">
         <v>1</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -2076,22 +2126,22 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C37" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D37" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E37" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F37">
         <v>1</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -2099,22 +2149,22 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C38" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D38" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E38" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F38">
         <v>2</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -2122,22 +2172,22 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C39" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D39" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F39">
         <v>2</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -2145,40 +2195,40 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C40" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D40" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F40">
         <v>2</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B41" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C41" s="7"/>
       <c r="D41" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E41" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F41">
         <v>2</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -2186,22 +2236,22 @@
         <v>38</v>
       </c>
       <c r="B42" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C42" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D42" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E42" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F42">
         <v>2</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -2209,22 +2259,22 @@
         <v>39</v>
       </c>
       <c r="B43" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C43" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D43" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E43" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F43">
         <v>2</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -2232,22 +2282,22 @@
         <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C44" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D44" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E44" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F44">
         <v>2</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -2255,22 +2305,22 @@
         <v>41</v>
       </c>
       <c r="B45" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C45" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D45" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F45">
         <v>2</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -2278,7 +2328,7 @@
         <v>42</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C46" s="7"/>
       <c r="D46" t="s">
@@ -2291,7 +2341,7 @@
         <v>1</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -2299,13 +2349,13 @@
         <v>43</v>
       </c>
       <c r="B47" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C47" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D47" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E47" t="s">
         <v>33</v>
@@ -2314,7 +2364,7 @@
         <v>1</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -2322,13 +2372,13 @@
         <v>44</v>
       </c>
       <c r="B48" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C48" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D48" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E48" t="s">
         <v>33</v>
@@ -2337,7 +2387,7 @@
         <v>2</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -2345,10 +2395,10 @@
         <v>45</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D49" s="8" t="s">
         <v>31</v>
@@ -2360,7 +2410,7 @@
         <v>1</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -2368,13 +2418,13 @@
         <v>46</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D50" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E50" s="8" t="s">
         <v>33</v>
@@ -2383,7 +2433,7 @@
         <v>1</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
@@ -2391,13 +2441,13 @@
         <v>47</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D51" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E51" s="8" t="s">
         <v>33</v>
@@ -2406,10 +2456,10 @@
         <v>1</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -2417,13 +2467,13 @@
         <v>48</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D52" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E52" s="8" t="s">
         <v>33</v>
@@ -2432,7 +2482,7 @@
         <v>1</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I52" s="8"/>
     </row>
@@ -2441,25 +2491,25 @@
         <v>49</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D53" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F53" s="8">
         <v>3</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I53" s="8" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -2467,25 +2517,25 @@
         <v>50</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D54" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E54" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="F54" s="8">
+        <v>2</v>
+      </c>
+      <c r="H54" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="I54" s="8" t="s">
         <v>169</v>
-      </c>
-      <c r="F54" s="8">
-        <v>2</v>
-      </c>
-      <c r="H54" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="I54" s="8" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -2493,13 +2543,13 @@
         <v>51</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D55" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E55" s="8" t="s">
         <v>33</v>
@@ -2508,10 +2558,10 @@
         <v>1</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
@@ -2519,10 +2569,10 @@
         <v>52</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D56" t="s">
         <v>31</v>
@@ -2534,10 +2584,10 @@
         <v>3</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I56" s="8" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
@@ -2545,13 +2595,13 @@
         <v>53</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D57" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E57" s="8" t="s">
         <v>32</v>
@@ -2560,10 +2610,10 @@
         <v>2</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>142</v>
+        <v>179</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
@@ -2571,13 +2621,13 @@
         <v>54</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D58" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E58" s="8" t="s">
         <v>32</v>
@@ -2586,24 +2636,22 @@
         <v>2</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="I58" s="8" t="s">
-        <v>141</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="I58" s="8"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>55</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D59" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E59" s="8" t="s">
         <v>33</v>
@@ -2612,10 +2660,10 @@
         <v>2</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I59" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
@@ -2623,22 +2671,22 @@
         <v>56</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D60" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F60" s="8">
         <v>3</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
@@ -2646,22 +2694,22 @@
         <v>57</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D61" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F61" s="8">
         <v>2</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
@@ -2669,22 +2717,25 @@
         <v>58</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D62" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F62" s="8">
         <v>1</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
+      </c>
+      <c r="I62" s="15" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
@@ -2692,20 +2743,20 @@
         <v>59</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F63" s="8">
         <v>3</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
@@ -2713,20 +2764,20 @@
         <v>60</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C64" s="9"/>
       <c r="D64" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F64" s="8">
         <v>1</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
@@ -2734,22 +2785,22 @@
         <v>61</v>
       </c>
       <c r="B65" s="14" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D65" t="s">
         <v>31</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F65" s="8">
         <v>1</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
@@ -2757,19 +2808,19 @@
         <v>62</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D66" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E66" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F66">
         <v>2</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
@@ -2777,13 +2828,13 @@
         <v>63</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D67" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E67" s="8" t="s">
         <v>32</v>
@@ -2792,10 +2843,10 @@
         <v>2</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I67" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
@@ -2803,13 +2854,13 @@
         <v>64</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D68" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E68" s="8" t="s">
         <v>32</v>
@@ -2818,31 +2869,33 @@
         <v>2</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="I68" s="8"/>
+        <v>175</v>
+      </c>
+      <c r="I68" s="8" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>65</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D69" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F69" s="8">
         <v>2</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I69" s="8"/>
     </row>
@@ -2851,22 +2904,22 @@
         <v>66</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D70" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F70" s="8">
         <v>3</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I70" s="8"/>
     </row>
@@ -2875,23 +2928,23 @@
         <v>67</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D71" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F71" s="8"/>
       <c r="H71" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I71" s="8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
@@ -2899,25 +2952,25 @@
         <v>68</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D72" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F72" s="8">
         <v>2</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I72" s="8" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
@@ -2925,10 +2978,10 @@
         <v>69</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D73" t="s">
         <v>31</v>
@@ -2940,12 +2993,15 @@
         <v>2</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
+      </c>
+      <c r="I73" s="8" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C77" t="s">
         <v>32</v>
@@ -2953,15 +3009,15 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
+        <v>47</v>
+      </c>
+      <c r="C78" t="s">
         <v>48</v>
-      </c>
-      <c r="C78" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C79" t="s">
         <v>33</v>
@@ -2969,10 +3025,10 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C80" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -3008,7 +3064,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="48" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>
@@ -3032,7 +3088,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -3049,13 +3105,13 @@
         <v>28</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F2" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="G2" s="10" t="s">
         <v>57</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -3063,16 +3119,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>166</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>168</v>
       </c>
       <c r="F3" s="8">
         <v>1</v>
@@ -3083,16 +3139,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F4" s="8">
         <v>1</v>
@@ -3103,22 +3159,22 @@
         <v>3</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F5" s="8">
         <v>1</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -3126,13 +3182,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F6" s="8">
         <v>1</v>
@@ -3143,19 +3199,19 @@
         <v>5</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F7" s="8">
         <v>3</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -3163,19 +3219,19 @@
         <v>6</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E8" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="F8" s="8">
+        <v>2</v>
+      </c>
+      <c r="G8" s="8" t="s">
         <v>169</v>
-      </c>
-      <c r="F8" s="8">
-        <v>2</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -3183,19 +3239,19 @@
         <v>7</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F9" s="8">
         <v>1</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -3203,10 +3259,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>32</v>
@@ -3215,7 +3271,7 @@
         <v>3</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -3223,10 +3279,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>32</v>
@@ -3235,7 +3291,7 @@
         <v>2</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -3243,10 +3299,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>32</v>
@@ -3255,7 +3311,7 @@
         <v>2</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -3263,19 +3319,19 @@
         <v>11</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F13" s="8">
         <v>2</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -3283,13 +3339,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F14" s="8">
         <v>3</v>
@@ -3300,13 +3356,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F15" s="8">
         <v>2</v>
@@ -3317,13 +3373,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F16" s="8">
         <v>1</v>
@@ -3334,10 +3390,10 @@
         <v>15</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F17" s="8">
         <v>3</v>
@@ -3345,10 +3401,10 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B18" s="8" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F18" s="8">
         <v>1</v>
@@ -3356,13 +3412,13 @@
     </row>
     <row r="19" spans="1:7" ht="30.75" x14ac:dyDescent="0.3">
       <c r="B19" s="14" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F19" s="8">
         <v>1</v>
@@ -3370,7 +3426,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -3387,13 +3443,13 @@
         <v>28</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F23" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="G23" s="10" t="s">
         <v>57</v>
-      </c>
-      <c r="G23" s="10" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -3401,19 +3457,19 @@
         <v>1</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F24" s="8">
         <v>2</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -3421,13 +3477,13 @@
         <v>2</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F25" s="8">
         <v>2</v>
@@ -3438,13 +3494,13 @@
         <v>3</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F26" s="8">
         <v>2</v>
@@ -3455,13 +3511,13 @@
         <v>4</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F27" s="8">
         <v>3</v>
@@ -3472,16 +3528,16 @@
         <v>5</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -3489,19 +3545,19 @@
         <v>6</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F29" s="8">
         <v>2</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -3509,10 +3565,10 @@
         <v>7</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E30" s="8" t="s">
         <v>32</v>

--- a/Verbesserungsliste.xlsx
+++ b/Verbesserungsliste.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\neume\Desktop\MCI\Robotik_Projekt\Optimierung-Laboraufgabe-Robotik\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B53C793B-B68C-44D4-9500-5D1F750015C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2D98EA8-931F-4B2F-A8C0-CA8AED61C47A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="189">
   <si>
     <t>Nr.</t>
   </si>
@@ -560,9 +560,6 @@
     <t>Check nochmal Ende Februar durchführen</t>
   </si>
   <si>
-    <t>Misumi für TCP-Spitze, lange Alu-Spitze verwerfen (wird ersetzt durch TeachingSpitze)</t>
-  </si>
-  <si>
     <t>wurde neu gedruckt</t>
   </si>
   <si>
@@ -578,13 +575,21 @@
     <t>Bereits für beide Anlagen umgesetzt</t>
   </si>
   <si>
-    <t>Wurde gedruckt (Qualtitä sehr schlecht --&gt; 3D nochmal anpassen)</t>
-  </si>
-  <si>
     <t>Wird direkt in die neue Abdeckung eingebaut</t>
   </si>
   <si>
     <t>Kommentare</t>
+  </si>
+  <si>
+    <t>Stück zur Kamerastabilisierung im Turm wurde konstruiert --&gt; Druck und Test ausstehend</t>
+  </si>
+  <si>
+    <t>Misumi für TCP-Spitze, lange Alu-Spitze verwerfen (wird ersetzt durch TeachingSpitze)
+Neue Halterung wurde konzipiert… muss noch gedruckt werden (M2.5 Gewinde !!!)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wurde gedruckt (Qualtitä sehr schlecht --&gt; 3D nochmal anpassen)
+Neue Abdeckung gedruckt ---&gt; besser </t>
   </si>
 </sst>
 </file>
@@ -691,7 +696,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -732,6 +737,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1258,7 +1266,7 @@
     <col min="6" max="6" width="9.85546875" customWidth="1"/>
     <col min="7" max="7" width="9.140625" style="5"/>
     <col min="8" max="8" width="13.140625" style="5" customWidth="1"/>
-    <col min="9" max="9" width="81" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="84.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1287,7 +1295,7 @@
         <v>36</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -1313,7 +1321,7 @@
         <v>29</v>
       </c>
       <c r="I2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -1391,7 +1399,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1402,7 +1410,7 @@
         <v>59</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E6" t="s">
         <v>32</v>
@@ -1413,8 +1421,8 @@
       <c r="G6" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="I6" t="s">
-        <v>185</v>
+      <c r="I6" s="16" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -1515,7 +1523,7 @@
         <v>29</v>
       </c>
       <c r="I10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -1564,7 +1572,7 @@
         <v>29</v>
       </c>
       <c r="I12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -1757,7 +1765,7 @@
         <v>29</v>
       </c>
       <c r="I20" s="15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -1806,7 +1814,7 @@
         <v>175</v>
       </c>
       <c r="I22" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -1820,7 +1828,7 @@
         <v>65</v>
       </c>
       <c r="D23" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="E23" t="s">
         <v>32</v>
@@ -1830,6 +1838,9 @@
       </c>
       <c r="G23" s="5" t="s">
         <v>175</v>
+      </c>
+      <c r="I23" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -1855,7 +1866,7 @@
         <v>175</v>
       </c>
       <c r="I24" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -2590,7 +2601,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>53</v>
       </c>
@@ -2601,7 +2612,7 @@
         <v>141</v>
       </c>
       <c r="D57" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="E57" s="8" t="s">
         <v>32</v>
@@ -2612,8 +2623,8 @@
       <c r="G57" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="I57" s="8" t="s">
-        <v>179</v>
+      <c r="I57" s="9" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">

--- a/Verbesserungsliste.xlsx
+++ b/Verbesserungsliste.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\neume\Desktop\MCI\Robotik_Projekt\Optimierung-Laboraufgabe-Robotik\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2D98EA8-931F-4B2F-A8C0-CA8AED61C47A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D63F531-8483-4909-87DA-B3EE71E083C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ToDos" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="195">
   <si>
     <t>Nr.</t>
   </si>
@@ -566,9 +566,6 @@
     <t>Schranke wurde im neuem Kameraturm nach vorne geschoben</t>
   </si>
   <si>
-    <t>Gedruckt (Test noch ausstehend)</t>
-  </si>
-  <si>
     <t>Adapter wird nicht mehr benötigt (Schnellwechsler im Einsatz)</t>
   </si>
   <si>
@@ -582,14 +579,38 @@
   </si>
   <si>
     <t>Stück zur Kamerastabilisierung im Turm wurde konstruiert --&gt; Druck und Test ausstehend</t>
-  </si>
-  <si>
-    <t>Misumi für TCP-Spitze, lange Alu-Spitze verwerfen (wird ersetzt durch TeachingSpitze)
-Neue Halterung wurde konzipiert… muss noch gedruckt werden (M2.5 Gewinde !!!)</t>
   </si>
   <si>
     <t xml:space="preserve">Wurde gedruckt (Qualtitä sehr schlecht --&gt; 3D nochmal anpassen)
 Neue Abdeckung gedruckt ---&gt; besser </t>
+  </si>
+  <si>
+    <t>Sprühdose (Weiß Matt) ist am Aufbau und kann umgesetzt werden</t>
+  </si>
+  <si>
+    <t>in progress</t>
+  </si>
+  <si>
+    <t>Frage ob wirklich eloxieren ? Kontrast schaut aktuell sehr gut aus… sonst zu schwarz !!!
+Hoher Zeitaufwand (gesamte Anlage demontieren)</t>
+  </si>
+  <si>
+    <t>Gewinde Nieten wurden vollständig gesetzt
+--&gt; Plexiglas muss noch geschnitten werden</t>
+  </si>
+  <si>
+    <t>Abdeckung Mitte steht noch aus (--&gt; Konzept mit Magneten testen)</t>
+  </si>
+  <si>
+    <t>Misumi für TCP-Spitze, lange Alu-Spitze verwerfen (wird ersetzt durch TeachingSpitze)
+Neue Halterung wurde konzipiert, gedruckt und getestet --&gt; funktioniert 
+Noch zwei weitere Teile drucken</t>
+  </si>
+  <si>
+    <t>Wurde gedruckt aber Lochabstände passen nicht…</t>
+  </si>
+  <si>
+    <t>Muss noch ein zweites Mal gedruckt werden :) aber test bisher gut</t>
   </si>
 </sst>
 </file>
@@ -696,7 +717,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -738,6 +759,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1295,7 +1319,7 @@
         <v>36</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -1321,7 +1345,7 @@
         <v>29</v>
       </c>
       <c r="I2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -1422,7 +1446,7 @@
         <v>29</v>
       </c>
       <c r="I6" s="16" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -1523,7 +1547,7 @@
         <v>29</v>
       </c>
       <c r="I10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -1537,7 +1561,7 @@
         <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E11" t="s">
         <v>33</v>
@@ -1572,7 +1596,7 @@
         <v>29</v>
       </c>
       <c r="I12" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -1765,7 +1789,7 @@
         <v>29</v>
       </c>
       <c r="I20" s="15" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -1840,7 +1864,7 @@
         <v>175</v>
       </c>
       <c r="I23" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -2389,7 +2413,7 @@
         <v>106</v>
       </c>
       <c r="D48" t="s">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="E48" t="s">
         <v>33</v>
@@ -2412,7 +2436,7 @@
         <v>163</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E49" s="8" t="s">
         <v>33</v>
@@ -2435,7 +2459,7 @@
         <v>160</v>
       </c>
       <c r="D50" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="E50" s="8" t="s">
         <v>33</v>
@@ -2484,7 +2508,7 @@
         <v>154</v>
       </c>
       <c r="D52" t="s">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="E52" s="8" t="s">
         <v>33</v>
@@ -2534,10 +2558,10 @@
         <v>149</v>
       </c>
       <c r="D54" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>167</v>
+        <v>32</v>
       </c>
       <c r="F54" s="8">
         <v>2</v>
@@ -2546,7 +2570,7 @@
         <v>175</v>
       </c>
       <c r="I54" s="8" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -2598,10 +2622,10 @@
         <v>175</v>
       </c>
       <c r="I56" s="8" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>53</v>
       </c>
@@ -2624,7 +2648,7 @@
         <v>175</v>
       </c>
       <c r="I57" s="9" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
@@ -2638,7 +2662,7 @@
         <v>112</v>
       </c>
       <c r="D58" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="E58" s="8" t="s">
         <v>32</v>
@@ -2649,9 +2673,11 @@
       <c r="G58" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="I58" s="8"/>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I58" s="8" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>55</v>
       </c>
@@ -2662,7 +2688,7 @@
         <v>137</v>
       </c>
       <c r="D59" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="E59" s="8" t="s">
         <v>33</v>
@@ -2673,8 +2699,8 @@
       <c r="G59" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="I59" s="8" t="s">
-        <v>136</v>
+      <c r="I59" s="9" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
@@ -2749,7 +2775,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>59</v>
       </c>
@@ -2769,6 +2795,9 @@
       <c r="H63" s="5" t="s">
         <v>175</v>
       </c>
+      <c r="I63" s="17" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64">
@@ -2845,7 +2874,7 @@
         <v>122</v>
       </c>
       <c r="D67" t="s">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="E67" s="8" t="s">
         <v>32</v>
@@ -2969,7 +2998,7 @@
         <v>114</v>
       </c>
       <c r="D72" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="E72" s="8" t="s">
         <v>173</v>
@@ -2981,7 +3010,7 @@
         <v>175</v>
       </c>
       <c r="I72" s="8" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
@@ -2995,7 +3024,7 @@
         <v>112</v>
       </c>
       <c r="D73" t="s">
-        <v>31</v>
+        <v>188</v>
       </c>
       <c r="E73" s="8" t="s">
         <v>32</v>

--- a/Verbesserungsliste.xlsx
+++ b/Verbesserungsliste.xlsx
@@ -5,18 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\neume\Desktop\MCI\Robotik_Projekt\Optimierung-Laboraufgabe-Robotik\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hanna\Documents\Optimierung-Laboraufgabe-Robotik\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F38C55E9-C96C-42B1-8AA4-DFA823F628B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CD3D344-3897-4D09-81C9-32F58E59DC37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ToDos" sheetId="1" r:id="rId1"/>
     <sheet name="Notes" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -1636,7 +1636,7 @@
         <v>55</v>
       </c>
       <c r="D16" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E16" t="s">
         <v>24</v>
@@ -2691,7 +2691,7 @@
         <v>150</v>
       </c>
       <c r="D61" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>24</v>
@@ -2904,7 +2904,7 @@
         <v>169</v>
       </c>
       <c r="D70" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E70" s="10" t="s">
         <v>24</v>

--- a/Verbesserungsliste.xlsx
+++ b/Verbesserungsliste.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hanna\Documents\Optimierung-Laboraufgabe-Robotik\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\neume\Desktop\MCI\Robotik_Projekt\Optimierung-Laboraufgabe-Robotik\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE9CFC57-9A57-484F-BB05-4CD588ECBD1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1194C4BE-D92A-443D-A724-4C00050EC883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ToDos" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="204">
   <si>
     <t>Nr.</t>
   </si>
@@ -452,191 +452,197 @@
     <t>Drucken, Spitze drehen, evtl. Verbessern?!</t>
   </si>
   <si>
+    <t>Abdeckungen + LED zweiter Roboter</t>
+  </si>
+  <si>
+    <t>Drucken, Montieren, Verkabeln</t>
+  </si>
+  <si>
+    <t>Abdeckung Mitte steht noch aus (--&gt; Konzept mit Magneten testen)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plexi Abdeckung </t>
+  </si>
+  <si>
+    <t>SPS Abdeckung von außen, 4 Löcher, 5mm</t>
+  </si>
+  <si>
+    <t>Gewinde Nieten wurden vollständig gesetzt
+--&gt; Plexiglas muss noch geschnitten werden</t>
+  </si>
+  <si>
+    <t>Labels außen</t>
+  </si>
+  <si>
+    <t>Beschriftungen drucken, um Layout zu testen</t>
+  </si>
+  <si>
+    <t>Rutsche testen</t>
+  </si>
+  <si>
+    <t>Testen ob keine Teile mehr hängen bleiben</t>
+  </si>
+  <si>
+    <t>Konstruktion checken</t>
+  </si>
+  <si>
+    <t>Sind alle Blechteile bereit und fehlerfrei?</t>
+  </si>
+  <si>
+    <t>Thomas/Olli</t>
+  </si>
+  <si>
+    <t>Check nochmal Ende Februar durchführen</t>
+  </si>
+  <si>
+    <t>Eloxieren inkl Demontage + Montage</t>
+  </si>
+  <si>
+    <t>Frage ob wirklich eloxieren ? Kontrast schaut aktuell sehr gut aus… sonst zu schwarz !!!
+Hoher Zeitaufwand (gesamte Anlage demontieren)</t>
+  </si>
+  <si>
+    <t>Inbetriebnahme</t>
+  </si>
+  <si>
+    <t>Alle</t>
+  </si>
+  <si>
+    <t>DOKU</t>
+  </si>
+  <si>
+    <t>Detailliert, so effektiv wie möglich das Gerät übergeben</t>
+  </si>
+  <si>
+    <t>Hardware-Doku über elektrische Verbindung, Netzwerk, Kamera, SPS etc. ist fertig LG Olli</t>
+  </si>
+  <si>
+    <t>Verbesserung erster Roboter</t>
+  </si>
+  <si>
+    <t>Kameraturm Base</t>
+  </si>
+  <si>
+    <t>Neue Version drucken und austauschen</t>
+  </si>
+  <si>
+    <t>gedruckt muss aber noch zusammengebaut werden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rutsche </t>
+  </si>
+  <si>
+    <t>Zweiter Aufbau erst testen, dann drucken</t>
+  </si>
+  <si>
+    <t>Blechbearbeitung</t>
+  </si>
+  <si>
+    <t>Löcher ETH/M12 Ports, Überstand oben abschneiden</t>
+  </si>
+  <si>
+    <t>Verkabelung</t>
+  </si>
+  <si>
+    <t>Neu verkabeln, wie beim Zweitaufbau</t>
+  </si>
+  <si>
+    <t>Teaching-Tools?</t>
+  </si>
+  <si>
+    <t>Verbessertes Montagesystem umsetzen</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>Kameraturm</t>
+  </si>
+  <si>
+    <t>Innen weiß lackieren? Einfacher als Multimaterial-Druck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Offen lassen </t>
+  </si>
+  <si>
+    <t>Abdeckungen + LED erster Roboter</t>
+  </si>
+  <si>
+    <t>in progress</t>
+  </si>
+  <si>
+    <t>Bereits gedruckt. Mittelteil mit Magneten muss noch getestet werden (alternative geschraubt)</t>
+  </si>
+  <si>
+    <t>3D Druck</t>
+  </si>
+  <si>
+    <t>Bleche</t>
+  </si>
+  <si>
+    <t>Stecker, Kabel</t>
+  </si>
+  <si>
+    <t>Elektrik</t>
+  </si>
+  <si>
+    <t>To-Dos zur Fertigstellung Zweitaufbau</t>
+  </si>
+  <si>
+    <t>Benjamins Kommentare</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>Olli</t>
+  </si>
+  <si>
+    <t>SPS Check</t>
+  </si>
+  <si>
+    <t>Verkabelung fertig, Inbetriebnahme OK, Funktionscheck ausstehend</t>
+  </si>
+  <si>
+    <t>Offen</t>
+  </si>
+  <si>
+    <t>Lösbar mittels richtigen CognexEinstellungen</t>
+  </si>
+  <si>
+    <t>Ausbaustufe: Harting-Stecker</t>
+  </si>
+  <si>
+    <t>Misumi für TCP-Spitze, lange Alu-Spitze verwerfen</t>
+  </si>
+  <si>
+    <t>Abdeckungen + LED</t>
+  </si>
+  <si>
+    <t>Ersten Druck behalten, erst wenn alles fertig ist neu drucken</t>
+  </si>
+  <si>
+    <t>Gewinde Nieten besorgen</t>
+  </si>
+  <si>
+    <t>To-Dos zur Verbesserung Erstaufbau</t>
+  </si>
+  <si>
+    <t>Bilder</t>
+  </si>
+  <si>
+    <t>Erklärung</t>
+  </si>
+  <si>
     <t>Misumi für TCP-Spitze, lange Alu-Spitze verwerfen (wird ersetzt durch TeachingSpitze)
 Neue Halterung wurde konzipiert, gedruckt und getestet --&gt; funktioniert 
-Noch zwei weitere Teile drucken</t>
-  </si>
-  <si>
-    <t>Abdeckungen + LED zweiter Roboter</t>
-  </si>
-  <si>
-    <t>Drucken, Montieren, Verkabeln</t>
-  </si>
-  <si>
-    <t>Abdeckung Mitte steht noch aus (--&gt; Konzept mit Magneten testen)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plexi Abdeckung </t>
-  </si>
-  <si>
-    <t>SPS Abdeckung von außen, 4 Löcher, 5mm</t>
-  </si>
-  <si>
-    <t>Gewinde Nieten wurden vollständig gesetzt
---&gt; Plexiglas muss noch geschnitten werden</t>
-  </si>
-  <si>
-    <t>Labels außen</t>
-  </si>
-  <si>
-    <t>Beschriftungen drucken, um Layout zu testen</t>
-  </si>
-  <si>
-    <t>Rutsche testen</t>
-  </si>
-  <si>
-    <t>Testen ob keine Teile mehr hängen bleiben</t>
-  </si>
-  <si>
-    <t>Konstruktion checken</t>
-  </si>
-  <si>
-    <t>Sind alle Blechteile bereit und fehlerfrei?</t>
-  </si>
-  <si>
-    <t>Thomas/Olli</t>
-  </si>
-  <si>
-    <t>Check nochmal Ende Februar durchführen</t>
-  </si>
-  <si>
-    <t>Eloxieren inkl Demontage + Montage</t>
-  </si>
-  <si>
-    <t>Frage ob wirklich eloxieren ? Kontrast schaut aktuell sehr gut aus… sonst zu schwarz !!!
-Hoher Zeitaufwand (gesamte Anlage demontieren)</t>
-  </si>
-  <si>
-    <t>Inbetriebnahme</t>
-  </si>
-  <si>
-    <t>Alle</t>
-  </si>
-  <si>
-    <t>DOKU</t>
-  </si>
-  <si>
-    <t>Detailliert, so effektiv wie möglich das Gerät übergeben</t>
-  </si>
-  <si>
-    <t>Hardware-Doku über elektrische Verbindung, Netzwerk, Kamera, SPS etc. ist fertig LG Olli</t>
-  </si>
-  <si>
-    <t>Verbesserung erster Roboter</t>
-  </si>
-  <si>
-    <t>Kameraturm Base</t>
-  </si>
-  <si>
-    <t>Neue Version drucken und austauschen</t>
-  </si>
-  <si>
-    <t>gedruckt muss aber noch zusammengebaut werden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rutsche </t>
-  </si>
-  <si>
-    <t>Zweiter Aufbau erst testen, dann drucken</t>
-  </si>
-  <si>
-    <t>Blechbearbeitung</t>
-  </si>
-  <si>
-    <t>Löcher ETH/M12 Ports, Überstand oben abschneiden</t>
-  </si>
-  <si>
-    <t>Verkabelung</t>
-  </si>
-  <si>
-    <t>Neu verkabeln, wie beim Zweitaufbau</t>
-  </si>
-  <si>
-    <t>Teaching-Tools?</t>
-  </si>
-  <si>
-    <t>Verbessertes Montagesystem umsetzen</t>
-  </si>
-  <si>
-    <t>?</t>
-  </si>
-  <si>
-    <t>Kameraturm</t>
-  </si>
-  <si>
-    <t>Innen weiß lackieren? Einfacher als Multimaterial-Druck</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Offen lassen </t>
-  </si>
-  <si>
-    <t>Abdeckungen + LED erster Roboter</t>
-  </si>
-  <si>
-    <t>in progress</t>
-  </si>
-  <si>
-    <t>Bereits gedruckt. Mittelteil mit Magneten muss noch getestet werden (alternative geschraubt)</t>
-  </si>
-  <si>
-    <t>3D Druck</t>
-  </si>
-  <si>
-    <t>Bleche</t>
-  </si>
-  <si>
-    <t>Stecker, Kabel</t>
-  </si>
-  <si>
-    <t>Elektrik</t>
-  </si>
-  <si>
-    <t>To-Dos zur Fertigstellung Zweitaufbau</t>
-  </si>
-  <si>
-    <t>Benjamins Kommentare</t>
-  </si>
-  <si>
-    <t>In Progress</t>
-  </si>
-  <si>
-    <t>Olli</t>
-  </si>
-  <si>
-    <t>SPS Check</t>
-  </si>
-  <si>
-    <t>Verkabelung fertig, Inbetriebnahme OK, Funktionscheck ausstehend</t>
-  </si>
-  <si>
-    <t>Offen</t>
-  </si>
-  <si>
-    <t>Lösbar mittels richtigen CognexEinstellungen</t>
-  </si>
-  <si>
-    <t>Ausbaustufe: Harting-Stecker</t>
-  </si>
-  <si>
-    <t>Misumi für TCP-Spitze, lange Alu-Spitze verwerfen</t>
-  </si>
-  <si>
-    <t>Abdeckungen + LED</t>
-  </si>
-  <si>
-    <t>Ersten Druck behalten, erst wenn alles fertig ist neu drucken</t>
-  </si>
-  <si>
-    <t>Gewinde Nieten besorgen</t>
-  </si>
-  <si>
-    <t>To-Dos zur Verbesserung Erstaufbau</t>
-  </si>
-  <si>
-    <t>Bilder</t>
-  </si>
-  <si>
-    <t>Erklärung</t>
+Nur Misumi TCP-Spitzen müssen bestellt werden !!!</t>
+  </si>
+  <si>
+    <t>Kabel</t>
+  </si>
+  <si>
+    <t>Verkabelung zweite Cognex Kamera / und allgemein Profinet Kabel, Encoder usw…</t>
   </si>
 </sst>
 </file>
@@ -790,7 +796,79 @@
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
     <cellStyle name="Standard 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="25">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.34998626667073579"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <sz val="11"/>
@@ -1043,8 +1121,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabelle1" displayName="Tabelle1" ref="A1:I74" totalsRowShown="0">
-  <autoFilter ref="A1:I74" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabelle1" displayName="Tabelle1" ref="A1:I75" totalsRowShown="0">
+  <autoFilter ref="A1:I75" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Nr."/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Thema"/>
@@ -1243,20 +1321,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I81"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="62.53125" customWidth="1"/>
-    <col min="3" max="3" width="60.1328125" customWidth="1"/>
-    <col min="4" max="4" width="11.73046875" customWidth="1"/>
-    <col min="5" max="5" width="19.265625" customWidth="1"/>
-    <col min="6" max="6" width="9.86328125" customWidth="1"/>
-    <col min="7" max="7" width="9.1328125" style="1"/>
-    <col min="8" max="8" width="13.1328125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="84.73046875" customWidth="1"/>
+    <col min="1" max="1" width="6.140625" customWidth="1"/>
+    <col min="2" max="2" width="62.5703125" customWidth="1"/>
+    <col min="3" max="3" width="60.140625" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="1"/>
+    <col min="8" max="8" width="13.140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="84.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1285,7 +1363,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1311,7 +1389,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1334,7 +1412,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1360,7 +1438,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1386,7 +1464,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1397,7 +1475,7 @@
         <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E6" t="s">
         <v>12</v>
@@ -1412,7 +1490,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1438,7 +1516,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1461,7 +1539,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1487,7 +1565,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1513,7 +1591,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1536,7 +1614,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1562,7 +1640,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1585,7 +1663,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1608,7 +1686,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1634,7 +1712,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1657,7 +1735,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1680,7 +1758,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1703,7 +1781,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1714,7 +1792,7 @@
         <v>60</v>
       </c>
       <c r="D19" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E19" t="s">
         <v>32</v>
@@ -1729,7 +1807,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1740,7 +1818,7 @@
         <v>63</v>
       </c>
       <c r="D20" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E20" t="s">
         <v>12</v>
@@ -1755,7 +1833,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1766,7 +1844,7 @@
         <v>66</v>
       </c>
       <c r="D21" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E21" t="s">
         <v>32</v>
@@ -1778,7 +1856,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1804,7 +1882,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1815,7 +1893,7 @@
         <v>72</v>
       </c>
       <c r="D23" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E23" t="s">
         <v>12</v>
@@ -1830,7 +1908,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1856,7 +1934,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B25" s="8" t="s">
         <v>77</v>
       </c>
@@ -1871,7 +1949,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>24</v>
       </c>
@@ -1894,7 +1972,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>25</v>
       </c>
@@ -1902,7 +1980,7 @@
         <v>80</v>
       </c>
       <c r="C27" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D27" t="s">
         <v>11</v>
@@ -1917,7 +1995,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26</v>
       </c>
@@ -1925,7 +2003,7 @@
         <v>81</v>
       </c>
       <c r="C28" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D28" t="s">
         <v>11</v>
@@ -1940,7 +2018,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>27</v>
       </c>
@@ -1963,7 +2041,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>28</v>
       </c>
@@ -1971,7 +2049,7 @@
         <v>84</v>
       </c>
       <c r="C30" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D30" t="s">
         <v>11</v>
@@ -1986,7 +2064,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>29</v>
       </c>
@@ -1994,7 +2072,7 @@
         <v>85</v>
       </c>
       <c r="C31" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D31" t="s">
         <v>11</v>
@@ -2009,7 +2087,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>30</v>
       </c>
@@ -2017,7 +2095,7 @@
         <v>86</v>
       </c>
       <c r="C32" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D32" t="s">
         <v>11</v>
@@ -2032,7 +2110,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>31</v>
       </c>
@@ -2040,7 +2118,7 @@
         <v>88</v>
       </c>
       <c r="C33" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D33" t="s">
         <v>11</v>
@@ -2055,13 +2133,13 @@
         <v>69</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B34" s="8" t="s">
         <v>89</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E34" t="s">
         <v>32</v>
@@ -2073,7 +2151,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>32</v>
       </c>
@@ -2084,7 +2162,7 @@
         <v>91</v>
       </c>
       <c r="D35" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E35" t="s">
         <v>32</v>
@@ -2096,7 +2174,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>33</v>
       </c>
@@ -2107,7 +2185,7 @@
         <v>93</v>
       </c>
       <c r="D36" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E36" t="s">
         <v>32</v>
@@ -2119,7 +2197,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>34</v>
       </c>
@@ -2130,7 +2208,7 @@
         <v>95</v>
       </c>
       <c r="D37" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E37" t="s">
         <v>32</v>
@@ -2142,7 +2220,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>35</v>
       </c>
@@ -2153,7 +2231,7 @@
         <v>87</v>
       </c>
       <c r="D38" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E38" t="s">
         <v>32</v>
@@ -2165,7 +2243,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>36</v>
       </c>
@@ -2176,7 +2254,7 @@
         <v>98</v>
       </c>
       <c r="D39" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E39" t="s">
         <v>32</v>
@@ -2188,7 +2266,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>37</v>
       </c>
@@ -2199,7 +2277,7 @@
         <v>98</v>
       </c>
       <c r="D40" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E40" t="s">
         <v>32</v>
@@ -2211,13 +2289,13 @@
         <v>69</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B41" s="8" t="s">
         <v>100</v>
       </c>
       <c r="C41" s="8"/>
       <c r="D41" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E41" t="s">
         <v>32</v>
@@ -2229,7 +2307,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>38</v>
       </c>
@@ -2240,7 +2318,7 @@
         <v>102</v>
       </c>
       <c r="D42" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E42" t="s">
         <v>32</v>
@@ -2252,7 +2330,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>39</v>
       </c>
@@ -2263,7 +2341,7 @@
         <v>104</v>
       </c>
       <c r="D43" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E43" t="s">
         <v>32</v>
@@ -2275,7 +2353,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>40</v>
       </c>
@@ -2286,7 +2364,7 @@
         <v>106</v>
       </c>
       <c r="D44" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E44" t="s">
         <v>32</v>
@@ -2298,7 +2376,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>41</v>
       </c>
@@ -2309,7 +2387,7 @@
         <v>108</v>
       </c>
       <c r="D45" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E45" t="s">
         <v>32</v>
@@ -2321,7 +2399,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>42</v>
       </c>
@@ -2342,7 +2420,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>43</v>
       </c>
@@ -2368,7 +2446,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>113</v>
       </c>
@@ -2388,7 +2466,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>44</v>
       </c>
@@ -2411,7 +2489,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>45</v>
       </c>
@@ -2434,7 +2512,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>46</v>
       </c>
@@ -2457,7 +2535,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>47</v>
       </c>
@@ -2483,7 +2561,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>48</v>
       </c>
@@ -2507,7 +2585,7 @@
       </c>
       <c r="I53" s="10"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>49</v>
       </c>
@@ -2533,7 +2611,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>50</v>
       </c>
@@ -2559,7 +2637,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>51</v>
       </c>
@@ -2585,7 +2663,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>52</v>
       </c>
@@ -2596,7 +2674,7 @@
         <v>137</v>
       </c>
       <c r="D57" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>12</v>
@@ -2611,7 +2689,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>53</v>
       </c>
@@ -2634,21 +2712,21 @@
         <v>69</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.45">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>54</v>
       </c>
       <c r="B59" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="C59" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="C59" s="11" t="s">
-        <v>143</v>
-      </c>
       <c r="D59" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>12</v>
@@ -2660,18 +2738,18 @@
         <v>69</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" ht="28.5" x14ac:dyDescent="0.45">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>55</v>
       </c>
       <c r="B60" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="C60" s="11" t="s">
         <v>145</v>
-      </c>
-      <c r="C60" s="11" t="s">
-        <v>146</v>
       </c>
       <c r="D60" t="s">
         <v>28</v>
@@ -2686,21 +2764,21 @@
         <v>69</v>
       </c>
       <c r="I60" s="11" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.45">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>56</v>
       </c>
       <c r="B61" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="C61" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="C61" s="11" t="s">
-        <v>149</v>
-      </c>
       <c r="D61" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>32</v>
@@ -2712,15 +2790,15 @@
         <v>69</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>57</v>
       </c>
       <c r="B62" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="C62" s="11" t="s">
         <v>150</v>
-      </c>
-      <c r="C62" s="11" t="s">
-        <v>151</v>
       </c>
       <c r="D62" t="s">
         <v>11</v>
@@ -2735,38 +2813,38 @@
         <v>69</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>58</v>
       </c>
       <c r="B63" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="C63" s="11" t="s">
         <v>152</v>
-      </c>
-      <c r="C63" s="11" t="s">
-        <v>153</v>
       </c>
       <c r="D63" t="s">
         <v>28</v>
       </c>
       <c r="E63" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="F63" s="10">
+        <v>1</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I63" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="F63" s="10">
-        <v>1</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I63" s="7" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" ht="28.5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="64" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>59</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C64" s="11"/>
       <c r="D64" t="s">
@@ -2782,22 +2860,22 @@
         <v>69</v>
       </c>
       <c r="I64" s="12" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.45">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>60</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C65" s="11"/>
       <c r="D65" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F65" s="10">
         <v>1</v>
@@ -2806,21 +2884,21 @@
         <v>69</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="16.899999999999999" x14ac:dyDescent="0.5">
+    <row r="66" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>61</v>
       </c>
       <c r="B66" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="C66" s="11" t="s">
         <v>160</v>
-      </c>
-      <c r="C66" s="11" t="s">
-        <v>161</v>
       </c>
       <c r="D66" t="s">
         <v>28</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F66" s="10">
         <v>1</v>
@@ -2829,21 +2907,21 @@
         <v>69</v>
       </c>
       <c r="I66" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.45">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>62</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D67" t="s">
         <v>23</v>
       </c>
       <c r="E67" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F67">
         <v>2</v>
@@ -2852,18 +2930,18 @@
         <v>69</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>63</v>
       </c>
       <c r="B68" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="C68" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="C68" s="11" t="s">
-        <v>165</v>
-      </c>
       <c r="D68" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E68" s="10" t="s">
         <v>12</v>
@@ -2875,18 +2953,18 @@
         <v>69</v>
       </c>
       <c r="I68" s="10" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.45">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>64</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D69" t="s">
         <v>28</v>
@@ -2901,18 +2979,18 @@
         <v>69</v>
       </c>
       <c r="I69" s="10" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.45">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>65</v>
       </c>
       <c r="B70" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="C70" s="11" t="s">
         <v>169</v>
-      </c>
-      <c r="C70" s="11" t="s">
-        <v>170</v>
       </c>
       <c r="D70" t="s">
         <v>23</v>
@@ -2928,15 +3006,15 @@
       </c>
       <c r="I70" s="10"/>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>66</v>
       </c>
       <c r="B71" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="C71" s="11" t="s">
         <v>171</v>
-      </c>
-      <c r="C71" s="11" t="s">
-        <v>172</v>
       </c>
       <c r="D71" t="s">
         <v>11</v>
@@ -2952,15 +3030,15 @@
       </c>
       <c r="I71" s="10"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>67</v>
       </c>
       <c r="B72" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="C72" s="11" t="s">
         <v>173</v>
-      </c>
-      <c r="C72" s="11" t="s">
-        <v>174</v>
       </c>
       <c r="D72" t="s">
         <v>23</v>
@@ -2973,24 +3051,24 @@
         <v>69</v>
       </c>
       <c r="I72" s="10" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.45">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>68</v>
       </c>
       <c r="B73" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="C73" s="11" t="s">
         <v>176</v>
-      </c>
-      <c r="C73" s="11" t="s">
-        <v>177</v>
       </c>
       <c r="D73" t="s">
         <v>28</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F73" s="10">
         <v>2</v>
@@ -3002,18 +3080,18 @@
         <v>132</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>69</v>
       </c>
       <c r="B74" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="C74" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="D74" t="s">
         <v>179</v>
-      </c>
-      <c r="C74" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="D74" t="s">
-        <v>180</v>
       </c>
       <c r="E74" s="10" t="s">
         <v>12</v>
@@ -3025,75 +3103,92 @@
         <v>69</v>
       </c>
       <c r="I74" s="10" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>70</v>
+      </c>
+      <c r="B75" t="s">
+        <v>202</v>
+      </c>
+      <c r="C75" t="s">
+        <v>203</v>
+      </c>
+      <c r="D75" t="s">
+        <v>23</v>
+      </c>
+      <c r="E75" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B78" t="s">
         <v>181</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="B78" t="s">
-        <v>182</v>
       </c>
       <c r="C78" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C79" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C80" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="81" spans="2:3" x14ac:dyDescent="0.45">
+    <row r="81" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C81" t="s">
         <v>24</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D74">
-    <cfRule type="cellIs" dxfId="15" priority="8" operator="equal">
+  <conditionalFormatting sqref="D2:D75">
+    <cfRule type="cellIs" dxfId="24" priority="8" operator="equal">
       <formula>"Not started"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="9" operator="equal">
       <formula>"In progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="10" operator="equal">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E74">
-    <cfRule type="containsText" dxfId="12" priority="2" operator="containsText" text="Alle">
+  <conditionalFormatting sqref="E2:E75">
+    <cfRule type="containsText" dxfId="21" priority="2" operator="containsText" text="Alle">
       <formula>NOT(ISERROR(SEARCH("Alle",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="3" operator="containsText" text="Offen lassen">
+    <cfRule type="containsText" dxfId="20" priority="3" operator="containsText" text="Offen lassen">
       <formula>NOT(ISERROR(SEARCH("Offen lassen",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="4" operator="containsText" text="Oskar">
+    <cfRule type="containsText" dxfId="19" priority="4" operator="containsText" text="Oskar">
       <formula>NOT(ISERROR(SEARCH("Oskar",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="5" operator="containsText" text="Hannah">
+    <cfRule type="containsText" dxfId="18" priority="5" operator="containsText" text="Hannah">
       <formula>NOT(ISERROR(SEARCH("Hannah",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="6" operator="containsText" text="Oliver">
+    <cfRule type="containsText" dxfId="17" priority="6" operator="containsText" text="Oliver">
       <formula>NOT(ISERROR(SEARCH("Oliver",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="Thomas">
+    <cfRule type="containsText" dxfId="16" priority="7" operator="containsText" text="Thomas">
       <formula>NOT(ISERROR(SEARCH("Thomas",E2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="47" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>
@@ -3103,24 +3198,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.53125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.53125" style="10"/>
-    <col min="2" max="2" width="37.1328125" style="10" customWidth="1"/>
-    <col min="3" max="3" width="35.53125" style="11" customWidth="1"/>
-    <col min="4" max="4" width="11.53125" style="10"/>
-    <col min="5" max="5" width="15.1328125" style="10" customWidth="1"/>
-    <col min="6" max="6" width="11.53125" style="10"/>
-    <col min="7" max="7" width="23.1328125" style="10" customWidth="1"/>
-    <col min="8" max="16384" width="11.53125" style="10"/>
+    <col min="1" max="1" width="11.5703125" style="10"/>
+    <col min="2" max="2" width="37.140625" style="10" customWidth="1"/>
+    <col min="3" max="3" width="35.5703125" style="11" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" style="10"/>
+    <col min="5" max="5" width="15.140625" style="10" customWidth="1"/>
+    <col min="6" max="6" width="11.5703125" style="10"/>
+    <col min="7" max="7" width="23.140625" style="10" customWidth="1"/>
+    <col min="8" max="16384" width="11.5703125" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>0</v>
       </c>
@@ -3140,10 +3235,10 @@
         <v>5</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="10">
         <v>1</v>
       </c>
@@ -3154,36 +3249,36 @@
         <v>118</v>
       </c>
       <c r="D3" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="E3" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="F3" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="10">
+        <v>2</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="F3" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A4" s="10">
-        <v>2</v>
-      </c>
-      <c r="B4" s="10" t="s">
+      <c r="C4" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>192</v>
-      </c>
       <c r="E4" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F4" s="10">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="10">
         <v>3</v>
       </c>
@@ -3194,10 +3289,10 @@
         <v>122</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F5" s="10">
         <v>1</v>
@@ -3206,7 +3301,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="10">
         <v>4</v>
       </c>
@@ -3217,13 +3312,13 @@
         <v>125</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F6" s="10">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="10">
         <v>5</v>
       </c>
@@ -3243,7 +3338,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <v>6</v>
       </c>
@@ -3260,10 +3355,10 @@
         <v>2</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="10">
         <v>7</v>
       </c>
@@ -3274,7 +3369,7 @@
         <v>134</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F9" s="10">
         <v>1</v>
@@ -3283,7 +3378,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <v>8</v>
       </c>
@@ -3300,10 +3395,10 @@
         <v>3</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="10">
         <v>9</v>
       </c>
@@ -3320,18 +3415,18 @@
         <v>2</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="10">
         <v>10</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>12</v>
@@ -3340,38 +3435,38 @@
         <v>2</v>
       </c>
       <c r="G12" s="10" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="10">
+        <v>11</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="F13" s="10">
+        <v>2</v>
+      </c>
+      <c r="G13" s="10" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A13" s="10">
-        <v>11</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="F13" s="10">
-        <v>2</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="10">
         <v>12</v>
       </c>
       <c r="B14" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="C14" s="11" t="s">
         <v>148</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>149</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>32</v>
@@ -3380,15 +3475,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="10">
         <v>13</v>
       </c>
       <c r="B15" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="C15" s="11" t="s">
         <v>150</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>151</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>24</v>
@@ -3397,29 +3492,29 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="10">
         <v>14</v>
       </c>
       <c r="B16" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="C16" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="E16" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="E16" s="10" t="s">
-        <v>154</v>
-      </c>
       <c r="F16" s="10">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="10">
         <v>15</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>128</v>
@@ -3428,37 +3523,37 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B18" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="E18" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="F18" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="30.75" x14ac:dyDescent="0.3">
+      <c r="B19" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="F18" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="28.9" x14ac:dyDescent="0.5">
-      <c r="B19" s="13" t="s">
+      <c r="C19" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="C19" s="11" t="s">
-        <v>161</v>
-      </c>
       <c r="E19" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F19" s="10">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>0</v>
       </c>
@@ -3478,18 +3573,18 @@
         <v>5</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="10">
         <v>1</v>
       </c>
       <c r="B24" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="C24" s="11" t="s">
         <v>164</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>165</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>32</v>
@@ -3498,18 +3593,18 @@
         <v>2</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="10">
         <v>2</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>32</v>
@@ -3518,15 +3613,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="10">
         <v>3</v>
       </c>
       <c r="B26" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="C26" s="11" t="s">
         <v>169</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>170</v>
       </c>
       <c r="E26" s="10" t="s">
         <v>32</v>
@@ -3535,15 +3630,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="10">
         <v>4</v>
       </c>
       <c r="B27" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="C27" s="11" t="s">
         <v>171</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>172</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>24</v>
@@ -3552,52 +3647,52 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="10">
         <v>5</v>
       </c>
       <c r="B28" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="C28" s="11" t="s">
         <v>173</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>174</v>
       </c>
       <c r="E28" s="10" t="s">
         <v>128</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="10">
         <v>6</v>
       </c>
       <c r="B29" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="C29" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="E29" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="E29" s="10" t="s">
-        <v>178</v>
-      </c>
       <c r="F29" s="10">
         <v>2</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="10">
         <v>7</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E30" s="10" t="s">
         <v>12</v>
@@ -3608,32 +3703,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2 D23">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="2" operator="equal">
       <formula>$D$3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="3" operator="equal">
       <formula>"In progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="4" operator="equal">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2 E23">
-    <cfRule type="containsText" dxfId="3" priority="5" operator="containsText" text="Oskar">
+    <cfRule type="containsText" dxfId="12" priority="5" operator="containsText" text="Oskar">
       <formula>NOT(ISERROR(SEARCH("Oskar",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="6" operator="containsText" text="Hannah">
+    <cfRule type="containsText" dxfId="11" priority="6" operator="containsText" text="Hannah">
       <formula>NOT(ISERROR(SEARCH("Hannah",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="7" operator="containsText" text="Oliver">
+    <cfRule type="containsText" dxfId="10" priority="7" operator="containsText" text="Oliver">
       <formula>NOT(ISERROR(SEARCH("Oliver",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="8" operator="containsText" text="Thomas">
+    <cfRule type="containsText" dxfId="9" priority="8" operator="containsText" text="Thomas">
       <formula>NOT(ISERROR(SEARCH("Thomas",E2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0249999999999999" bottom="1.0249999999999999" header="0.78749999999999998" footer="0.78749999999999998"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;"Arial,Regular"&amp;10&amp;Kffffff&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Arial,Regular"&amp;10&amp;KffffffPage &amp;P</oddFooter>

--- a/Verbesserungsliste.xlsx
+++ b/Verbesserungsliste.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\neume\Desktop\MCI\Robotik_Projekt\Optimierung-Laboraufgabe-Robotik\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1194C4BE-D92A-443D-A724-4C00050EC883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{206CFD37-8F06-43E8-89AD-D745D773B37F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="203">
   <si>
     <t>Nr.</t>
   </si>
@@ -566,9 +566,6 @@
   </si>
   <si>
     <t>Abdeckungen + LED erster Roboter</t>
-  </si>
-  <si>
-    <t>in progress</t>
   </si>
   <si>
     <t>Bereits gedruckt. Mittelteil mit Magneten muss noch getestet werden (alternative geschraubt)</t>
@@ -796,79 +793,7 @@
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
     <cellStyle name="Standard 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
   </cellStyles>
-  <dxfs count="25">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="16">
     <dxf>
       <font>
         <sz val="11"/>
@@ -1980,7 +1905,7 @@
         <v>80</v>
       </c>
       <c r="C27" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D27" t="s">
         <v>11</v>
@@ -2003,7 +1928,7 @@
         <v>81</v>
       </c>
       <c r="C28" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D28" t="s">
         <v>11</v>
@@ -2049,7 +1974,7 @@
         <v>84</v>
       </c>
       <c r="C30" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D30" t="s">
         <v>11</v>
@@ -2072,7 +1997,7 @@
         <v>85</v>
       </c>
       <c r="C31" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D31" t="s">
         <v>11</v>
@@ -2095,7 +2020,7 @@
         <v>86</v>
       </c>
       <c r="C32" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D32" t="s">
         <v>11</v>
@@ -2118,7 +2043,7 @@
         <v>88</v>
       </c>
       <c r="C33" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D33" t="s">
         <v>11</v>
@@ -2712,7 +2637,7 @@
         <v>69</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
@@ -2967,7 +2892,7 @@
         <v>164</v>
       </c>
       <c r="D69" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>12</v>
@@ -3091,7 +3016,7 @@
         <v>142</v>
       </c>
       <c r="D74" t="s">
-        <v>179</v>
+        <v>11</v>
       </c>
       <c r="E74" s="10" t="s">
         <v>12</v>
@@ -3103,7 +3028,7 @@
         <v>69</v>
       </c>
       <c r="I74" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
@@ -3111,10 +3036,10 @@
         <v>70</v>
       </c>
       <c r="B75" t="s">
+        <v>201</v>
+      </c>
+      <c r="C75" t="s">
         <v>202</v>
-      </c>
-      <c r="C75" t="s">
-        <v>203</v>
       </c>
       <c r="D75" t="s">
         <v>23</v>
@@ -3125,7 +3050,7 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C78" t="s">
         <v>12</v>
@@ -3133,7 +3058,7 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C79" t="s">
         <v>32</v>
@@ -3141,7 +3066,7 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C80" t="s">
         <v>17</v>
@@ -3149,7 +3074,7 @@
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C81" t="s">
         <v>24</v>
@@ -3157,33 +3082,33 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D75">
-    <cfRule type="cellIs" dxfId="24" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="8" operator="equal">
       <formula>"Not started"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="9" operator="equal">
       <formula>"In progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="10" operator="equal">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E75">
-    <cfRule type="containsText" dxfId="21" priority="2" operator="containsText" text="Alle">
+    <cfRule type="containsText" dxfId="12" priority="2" operator="containsText" text="Alle">
       <formula>NOT(ISERROR(SEARCH("Alle",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="3" operator="containsText" text="Offen lassen">
+    <cfRule type="containsText" dxfId="11" priority="3" operator="containsText" text="Offen lassen">
       <formula>NOT(ISERROR(SEARCH("Offen lassen",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="19" priority="4" operator="containsText" text="Oskar">
+    <cfRule type="containsText" dxfId="10" priority="4" operator="containsText" text="Oskar">
       <formula>NOT(ISERROR(SEARCH("Oskar",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="5" operator="containsText" text="Hannah">
+    <cfRule type="containsText" dxfId="9" priority="5" operator="containsText" text="Hannah">
       <formula>NOT(ISERROR(SEARCH("Hannah",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="17" priority="6" operator="containsText" text="Oliver">
+    <cfRule type="containsText" dxfId="8" priority="6" operator="containsText" text="Oliver">
       <formula>NOT(ISERROR(SEARCH("Oliver",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="7" operator="containsText" text="Thomas">
+    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="Thomas">
       <formula>NOT(ISERROR(SEARCH("Thomas",E2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3212,7 +3137,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -3235,7 +3160,7 @@
         <v>5</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -3249,10 +3174,10 @@
         <v>118</v>
       </c>
       <c r="D3" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="E3" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="F3" s="10">
         <v>1</v>
@@ -3263,16 +3188,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="C4" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>191</v>
-      </c>
       <c r="E4" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F4" s="10">
         <v>1</v>
@@ -3289,10 +3214,10 @@
         <v>122</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F5" s="10">
         <v>1</v>
@@ -3312,7 +3237,7 @@
         <v>125</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F6" s="10">
         <v>1</v>
@@ -3355,7 +3280,7 @@
         <v>2</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -3369,7 +3294,7 @@
         <v>134</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F9" s="10">
         <v>1</v>
@@ -3395,7 +3320,7 @@
         <v>3</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -3415,7 +3340,7 @@
         <v>2</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -3423,7 +3348,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>142</v>
@@ -3435,7 +3360,7 @@
         <v>2</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -3449,13 +3374,13 @@
         <v>145</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F13" s="10">
         <v>2</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -3550,7 +3475,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -3573,7 +3498,7 @@
         <v>5</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -3681,7 +3606,7 @@
         <v>2</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -3689,7 +3614,7 @@
         <v>7</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C30" s="11" t="s">
         <v>142</v>
@@ -3703,27 +3628,27 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2 D23">
-    <cfRule type="cellIs" dxfId="15" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>$D$3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
       <formula>"In progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2 E23">
-    <cfRule type="containsText" dxfId="12" priority="5" operator="containsText" text="Oskar">
+    <cfRule type="containsText" dxfId="3" priority="5" operator="containsText" text="Oskar">
       <formula>NOT(ISERROR(SEARCH("Oskar",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="6" operator="containsText" text="Hannah">
+    <cfRule type="containsText" dxfId="2" priority="6" operator="containsText" text="Hannah">
       <formula>NOT(ISERROR(SEARCH("Hannah",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="7" operator="containsText" text="Oliver">
+    <cfRule type="containsText" dxfId="1" priority="7" operator="containsText" text="Oliver">
       <formula>NOT(ISERROR(SEARCH("Oliver",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="8" operator="containsText" text="Thomas">
+    <cfRule type="containsText" dxfId="0" priority="8" operator="containsText" text="Thomas">
       <formula>NOT(ISERROR(SEARCH("Thomas",E2)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Verbesserungsliste.xlsx
+++ b/Verbesserungsliste.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\neume\Desktop\MCI\Robotik_Projekt\Optimierung-Laboraufgabe-Robotik\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{206CFD37-8F06-43E8-89AD-D745D773B37F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{463E474D-69FF-4C2D-91AC-A96E13E8205C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ToDos" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="215">
   <si>
     <t>Nr.</t>
   </si>
@@ -101,9 +101,6 @@
   </si>
   <si>
     <t>Hannah</t>
-  </si>
-  <si>
-    <t>Plexiglas mit Nieten</t>
   </si>
   <si>
     <t>Abdeckungen</t>
@@ -365,9 +362,6 @@
     <t>Encoder-Signal und Trigger-Signal an der CNV-Karte von IRB...67 prüfen</t>
   </si>
   <si>
-    <t>ENC A+B Signal des SPS_67 Aufbaus kommt noch nicht (EL2521 konfigurieren), Lichtschranke Trigger kommt komischerweise auch nicht -testen</t>
-  </si>
-  <si>
     <t>SPS: LED Grün/Rot konfigurieren und in Profinet einbinden</t>
   </si>
   <si>
@@ -425,9 +419,6 @@
     <t>Kameraturm + Kamera-Halterung drucken, Kamera-Halterung in CAD verstärken, innen weiß lackieren</t>
   </si>
   <si>
-    <t>Sprühdose (Weiß Matt) ist am Aufbau und kann umgesetzt werden</t>
-  </si>
-  <si>
     <t>3D-Druck restliche Teileträger + Montage</t>
   </si>
   <si>
@@ -467,10 +458,6 @@
     <t>SPS Abdeckung von außen, 4 Löcher, 5mm</t>
   </si>
   <si>
-    <t>Gewinde Nieten wurden vollständig gesetzt
---&gt; Plexiglas muss noch geschnitten werden</t>
-  </si>
-  <si>
     <t>Labels außen</t>
   </si>
   <si>
@@ -498,10 +485,6 @@
     <t>Eloxieren inkl Demontage + Montage</t>
   </si>
   <si>
-    <t>Frage ob wirklich eloxieren ? Kontrast schaut aktuell sehr gut aus… sonst zu schwarz !!!
-Hoher Zeitaufwand (gesamte Anlage demontieren)</t>
-  </si>
-  <si>
     <t>Inbetriebnahme</t>
   </si>
   <si>
@@ -571,18 +554,6 @@
     <t>Bereits gedruckt. Mittelteil mit Magneten muss noch getestet werden (alternative geschraubt)</t>
   </si>
   <si>
-    <t>3D Druck</t>
-  </si>
-  <si>
-    <t>Bleche</t>
-  </si>
-  <si>
-    <t>Stecker, Kabel</t>
-  </si>
-  <si>
-    <t>Elektrik</t>
-  </si>
-  <si>
     <t>To-Dos zur Fertigstellung Zweitaufbau</t>
   </si>
   <si>
@@ -629,24 +600,122 @@
   </si>
   <si>
     <t>Erklärung</t>
+  </si>
+  <si>
+    <t>Kabel</t>
+  </si>
+  <si>
+    <t>Verkabelung zweite Cognex Kamera / und allgemein Profinet Kabel, Encoder usw…</t>
+  </si>
+  <si>
+    <t>Teile bestellen (Karten bei Beckhoff)</t>
+  </si>
+  <si>
+    <t>SPS-Halterung nach oben versetzen – Zwischenadapter gedruckt</t>
+  </si>
+  <si>
+    <t>Sprühdose (Weiß Matt) ist am Aufbau und kann umgesetzt werden
+Wenn noch Zeit umsetzen (aber aufjedenfall einstellungen in Cognex Anleitung übernehmen)</t>
   </si>
   <si>
     <t>Misumi für TCP-Spitze, lange Alu-Spitze verwerfen (wird ersetzt durch TeachingSpitze)
 Neue Halterung wurde konzipiert, gedruckt und getestet --&gt; funktioniert 
-Nur Misumi TCP-Spitzen müssen bestellt werden !!!</t>
-  </si>
-  <si>
-    <t>Kabel</t>
-  </si>
-  <si>
-    <t>Verkabelung zweite Cognex Kamera / und allgemein Profinet Kabel, Encoder usw…</t>
+Nur Misumi TCP-Spitzen müssen bestellt werden !!!
+Mail an Benjamin</t>
+  </si>
+  <si>
+    <t>Gewinde Nieten wurden vollständig gesetzt
+--&gt; Plexiglas muss noch geschnitten werden
+wenn noch Zeit</t>
+  </si>
+  <si>
+    <t>Frage ob wirklich eloxieren ? Kontrast schaut aktuell sehr gut aus… sonst zu schwarz !!!
+Hoher Zeitaufwand (gesamte Anlage demontieren)
+Wird wenndann im Sommer umgesetzt</t>
+  </si>
+  <si>
+    <t>Olli fragen, was damit gemeint ist</t>
+  </si>
+  <si>
+    <t>Bauteile (good, not good)</t>
+  </si>
+  <si>
+    <t>Noch kontrollieren bzw. drucken</t>
+  </si>
+  <si>
+    <t>PDF in der Kiste</t>
+  </si>
+  <si>
+    <t>Inhalt der Kiste aufschreiben (standardmäßiger Inhalt)</t>
+  </si>
+  <si>
+    <t>Eine Kiste mit allen Ersatzteilen usw.</t>
+  </si>
+  <si>
+    <t>Rutsche Aufbau</t>
+  </si>
+  <si>
+    <t>Nochmal drucken</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ENC A+B Signal des SPS_67 Aufbaus kommt noch nicht (EL2521 konfigurieren), Lichtschranke Trigger kommt komischerweise auch nicht -testen
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Parametrierung der Karten passt nicht</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Gespräch mit Olli: welche Karte und/oder LevelShifter nachbestellt werden muss (welche Kombo funtioniert)
+Tobias Obwechser, Olli, Oskar Online Meeting durchführen, um Problem zu lösen</t>
+    </r>
+  </si>
+  <si>
+    <t>Oliver/Oskar</t>
+  </si>
+  <si>
+    <t>Bestellliste</t>
+  </si>
+  <si>
+    <t>PE Doppelstockklemmen (5x)
+Zahlen Beschriftung 1-9 (einmal die 1)
+Ethernetkabel (1x 30 cm) und (1x 50cm) und (1x 100cm)
+Steckkarten bestellen (Hannah/Oskar klären mit Olli welche Karte)
+Misumi Spitzen (5x)</t>
+  </si>
+  <si>
+    <t>Plexiglas mit Nieten
+Wird nicht mehr umgesetzt (abgesprochen mit Benjamin)</t>
+  </si>
+  <si>
+    <t>Zweite Box ist im Laborschrank mit zugehörigen Kabel (Gut/Schlechtteile noch aufteile und dazulegen)</t>
+  </si>
+  <si>
+    <t>Ersatzteilkiste</t>
+  </si>
+  <si>
+    <t>Am Ende alles in eine Kiste</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -684,13 +753,31 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="4">
@@ -741,7 +828,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -787,6 +874,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1046,8 +1139,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabelle1" displayName="Tabelle1" ref="A1:I75" totalsRowShown="0">
-  <autoFilter ref="A1:I75" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabelle1" displayName="Tabelle1" ref="A1:I78" totalsRowShown="0">
+  <autoFilter ref="A1:I78" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Nr."/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Thema"/>
@@ -1245,7 +1338,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I81"/>
+  <dimension ref="A1:I85"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.140625" customWidth="1"/>
@@ -1256,7 +1349,7 @@
     <col min="6" max="6" width="9.85546875" customWidth="1"/>
     <col min="7" max="7" width="9.140625" style="1"/>
     <col min="8" max="8" width="13.140625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="84.7109375" customWidth="1"/>
+    <col min="9" max="9" width="97.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1363,7 +1456,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1377,7 +1470,7 @@
         <v>23</v>
       </c>
       <c r="E5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F5">
         <v>3</v>
@@ -1385,8 +1478,8 @@
       <c r="H5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I5" t="s">
-        <v>25</v>
+      <c r="I5" s="6" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -1394,10 +1487,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
         <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>27</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
@@ -1412,7 +1505,7 @@
         <v>13</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -1420,16 +1513,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
         <v>30</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
         <v>31</v>
-      </c>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" t="s">
-        <v>32</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -1438,7 +1531,7 @@
         <v>13</v>
       </c>
       <c r="I7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -1446,10 +1539,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
         <v>34</v>
-      </c>
-      <c r="C8" t="s">
-        <v>35</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
@@ -1469,16 +1562,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" t="s">
         <v>36</v>
       </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F9">
         <v>2</v>
@@ -1487,7 +1580,7 @@
         <v>13</v>
       </c>
       <c r="I9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -1495,10 +1588,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" t="s">
         <v>39</v>
-      </c>
-      <c r="C10" t="s">
-        <v>40</v>
       </c>
       <c r="D10" t="s">
         <v>11</v>
@@ -1513,7 +1606,7 @@
         <v>13</v>
       </c>
       <c r="I10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -1521,10 +1614,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" t="s">
         <v>42</v>
-      </c>
-      <c r="C11" t="s">
-        <v>43</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
@@ -1544,10 +1637,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" t="s">
         <v>44</v>
-      </c>
-      <c r="C12" t="s">
-        <v>45</v>
       </c>
       <c r="D12" t="s">
         <v>11</v>
@@ -1562,7 +1655,7 @@
         <v>13</v>
       </c>
       <c r="I12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -1570,10 +1663,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" t="s">
         <v>47</v>
-      </c>
-      <c r="C13" t="s">
-        <v>48</v>
       </c>
       <c r="D13" t="s">
         <v>11</v>
@@ -1593,10 +1686,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" t="s">
         <v>49</v>
-      </c>
-      <c r="C14" t="s">
-        <v>50</v>
       </c>
       <c r="D14" t="s">
         <v>11</v>
@@ -1616,10 +1709,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" t="s">
         <v>51</v>
-      </c>
-      <c r="C15" t="s">
-        <v>52</v>
       </c>
       <c r="D15" t="s">
         <v>11</v>
@@ -1634,7 +1727,7 @@
         <v>13</v>
       </c>
       <c r="I15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -1642,13 +1735,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" t="s">
         <v>54</v>
       </c>
-      <c r="C16" t="s">
-        <v>55</v>
-      </c>
       <c r="D16" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="E16" t="s">
         <v>24</v>
@@ -1658,6 +1751,9 @@
       </c>
       <c r="G16" s="1" t="s">
         <v>13</v>
+      </c>
+      <c r="I16" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -1665,10 +1761,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D17" t="s">
         <v>11</v>
@@ -1688,10 +1784,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" t="s">
         <v>57</v>
-      </c>
-      <c r="C18" t="s">
-        <v>58</v>
       </c>
       <c r="D18" t="s">
         <v>11</v>
@@ -1711,16 +1807,16 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" t="s">
         <v>59</v>
       </c>
-      <c r="C19" t="s">
-        <v>60</v>
-      </c>
       <c r="D19" t="s">
         <v>11</v>
       </c>
       <c r="E19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F19">
         <v>3</v>
@@ -1729,7 +1825,7 @@
         <v>13</v>
       </c>
       <c r="I19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -1737,10 +1833,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" t="s">
         <v>62</v>
-      </c>
-      <c r="C20" t="s">
-        <v>63</v>
       </c>
       <c r="D20" t="s">
         <v>11</v>
@@ -1755,7 +1851,7 @@
         <v>13</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -1763,16 +1859,16 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" t="s">
         <v>65</v>
       </c>
-      <c r="C21" t="s">
-        <v>66</v>
-      </c>
       <c r="D21" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F21">
         <v>2</v>
@@ -1786,10 +1882,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" t="s">
         <v>67</v>
-      </c>
-      <c r="C22" t="s">
-        <v>68</v>
       </c>
       <c r="D22" t="s">
         <v>11</v>
@@ -1801,10 +1897,10 @@
         <v>1</v>
       </c>
       <c r="G22" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I22" t="s">
         <v>69</v>
-      </c>
-      <c r="I22" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -1812,10 +1908,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23" t="s">
         <v>71</v>
-      </c>
-      <c r="C23" t="s">
-        <v>72</v>
       </c>
       <c r="D23" t="s">
         <v>11</v>
@@ -1827,10 +1923,10 @@
         <v>1</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -1838,10 +1934,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" t="s">
         <v>74</v>
-      </c>
-      <c r="C24" t="s">
-        <v>75</v>
       </c>
       <c r="D24" t="s">
         <v>11</v>
@@ -1853,15 +1949,18 @@
         <v>3</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" s="8" t="s">
         <v>76</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B25" s="8" t="s">
-        <v>77</v>
       </c>
       <c r="C25" s="8"/>
       <c r="D25" t="s">
@@ -1876,13 +1975,13 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" t="s">
+        <v>77</v>
+      </c>
+      <c r="C26" t="s">
         <v>78</v>
-      </c>
-      <c r="C26" t="s">
-        <v>79</v>
       </c>
       <c r="D26" t="s">
         <v>11</v>
@@ -1894,18 +1993,18 @@
         <v>2</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C27" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="D27" t="s">
         <v>11</v>
@@ -1917,18 +2016,18 @@
         <v>3</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C28" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="D28" t="s">
         <v>11</v>
@@ -1940,18 +2039,18 @@
         <v>1</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29" t="s">
+        <v>81</v>
+      </c>
+      <c r="C29" t="s">
         <v>82</v>
-      </c>
-      <c r="C29" t="s">
-        <v>83</v>
       </c>
       <c r="D29" t="s">
         <v>11</v>
@@ -1963,18 +2062,18 @@
         <v>1</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C30" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="D30" t="s">
         <v>11</v>
@@ -1986,18 +2085,18 @@
         <v>1</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C31" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="D31" t="s">
         <v>11</v>
@@ -2009,18 +2108,18 @@
         <v>1</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C32" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="D32" t="s">
         <v>11</v>
@@ -2032,18 +2131,18 @@
         <v>1</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C33" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="D33" t="s">
         <v>11</v>
@@ -2055,285 +2154,291 @@
         <v>3</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
       <c r="B34" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E34" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F34">
         <v>1</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B35" t="s">
+        <v>89</v>
+      </c>
+      <c r="C35" t="s">
         <v>90</v>
       </c>
-      <c r="C35" t="s">
-        <v>91</v>
-      </c>
       <c r="D35" t="s">
         <v>11</v>
       </c>
       <c r="E35" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F35">
         <v>1</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B36" t="s">
+        <v>91</v>
+      </c>
+      <c r="C36" t="s">
         <v>92</v>
       </c>
-      <c r="C36" t="s">
-        <v>93</v>
-      </c>
       <c r="D36" t="s">
         <v>11</v>
       </c>
       <c r="E36" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F36">
         <v>1</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B37" t="s">
+        <v>93</v>
+      </c>
+      <c r="C37" t="s">
         <v>94</v>
       </c>
-      <c r="C37" t="s">
-        <v>95</v>
-      </c>
       <c r="D37" t="s">
         <v>11</v>
       </c>
       <c r="E37" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F37">
         <v>1</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C38" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F38">
         <v>2</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B39" t="s">
+        <v>96</v>
+      </c>
+      <c r="C39" t="s">
         <v>97</v>
       </c>
-      <c r="C39" t="s">
-        <v>98</v>
-      </c>
       <c r="D39" t="s">
         <v>11</v>
       </c>
       <c r="E39" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F39">
         <v>2</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B40" t="s">
+        <v>98</v>
+      </c>
+      <c r="C40" t="s">
+        <v>97</v>
+      </c>
+      <c r="D40" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" t="s">
+        <v>31</v>
+      </c>
+      <c r="F40">
+        <v>2</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" s="8" t="s">
         <v>99</v>
-      </c>
-      <c r="C40" t="s">
-        <v>98</v>
-      </c>
-      <c r="D40" t="s">
-        <v>11</v>
-      </c>
-      <c r="E40" t="s">
-        <v>32</v>
-      </c>
-      <c r="F40">
-        <v>2</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B41" s="8" t="s">
-        <v>100</v>
       </c>
       <c r="C41" s="8"/>
       <c r="D41" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E41" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F41">
         <v>2</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B42" t="s">
+        <v>100</v>
+      </c>
+      <c r="C42" t="s">
         <v>101</v>
       </c>
-      <c r="C42" t="s">
-        <v>102</v>
-      </c>
       <c r="D42" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E42" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F42">
         <v>2</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B43" t="s">
+        <v>102</v>
+      </c>
+      <c r="C43" t="s">
         <v>103</v>
       </c>
-      <c r="C43" t="s">
-        <v>104</v>
-      </c>
       <c r="D43" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E43" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F43">
         <v>2</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B44" t="s">
+        <v>104</v>
+      </c>
+      <c r="C44" t="s">
         <v>105</v>
       </c>
-      <c r="C44" t="s">
-        <v>106</v>
-      </c>
       <c r="D44" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E44" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F44">
         <v>2</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B45" t="s">
+        <v>106</v>
+      </c>
+      <c r="C45" t="s">
         <v>107</v>
       </c>
-      <c r="C45" t="s">
-        <v>108</v>
-      </c>
       <c r="D45" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E45" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F45">
         <v>2</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C46" s="8"/>
       <c r="D46" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E46" t="s">
         <v>17</v>
@@ -2342,41 +2447,44 @@
         <v>1</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B47" t="s">
+        <v>109</v>
+      </c>
+      <c r="C47" t="s">
         <v>110</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
+        <v>27</v>
+      </c>
+      <c r="E47" t="s">
+        <v>208</v>
+      </c>
+      <c r="F47">
+        <v>1</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I47" s="18" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
         <v>111</v>
       </c>
-      <c r="D47" t="s">
-        <v>23</v>
-      </c>
-      <c r="E47" t="s">
-        <v>17</v>
-      </c>
-      <c r="F47">
-        <v>1</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I47" s="6" t="s">
+      <c r="C48" t="s">
         <v>112</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B48" t="s">
-        <v>113</v>
-      </c>
-      <c r="C48" t="s">
-        <v>114</v>
       </c>
       <c r="D48" t="s">
         <v>11</v>
@@ -2388,18 +2496,18 @@
         <v>2</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C49" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D49" t="s">
         <v>11</v>
@@ -2411,18 +2519,18 @@
         <v>2</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D50" s="10" t="s">
         <v>11</v>
@@ -2434,21 +2542,21 @@
         <v>1</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D51" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>17</v>
@@ -2457,18 +2565,18 @@
         <v>1</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D52" t="s">
         <v>11</v>
@@ -2480,21 +2588,21 @@
         <v>1</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I52" s="10" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D53" t="s">
         <v>11</v>
@@ -2506,48 +2614,48 @@
         <v>1</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I53" s="10"/>
     </row>
     <row r="54" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D54" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>128</v>
+        <v>12</v>
       </c>
       <c r="F54" s="10">
         <v>3</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I54" s="10" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="C55" s="11" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="55" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <v>50</v>
-      </c>
-      <c r="B55" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="C55" s="11" t="s">
-        <v>131</v>
-      </c>
       <c r="D55" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>12</v>
@@ -2556,21 +2664,21 @@
         <v>2</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I55" s="10" t="s">
-        <v>132</v>
+        <v>68</v>
+      </c>
+      <c r="I55" s="11" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D56" t="s">
         <v>11</v>
@@ -2582,21 +2690,21 @@
         <v>1</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I56" s="10" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D57" t="s">
         <v>11</v>
@@ -2608,24 +2716,24 @@
         <v>3</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D58" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E58" s="10" t="s">
         <v>12</v>
@@ -2634,21 +2742,21 @@
         <v>2</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I58" s="11" t="s">
-        <v>200</v>
+        <v>68</v>
+      </c>
+      <c r="I58" s="19" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D59" t="s">
         <v>11</v>
@@ -2660,24 +2768,24 @@
         <v>2</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D60" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E60" s="10" t="s">
         <v>17</v>
@@ -2686,44 +2794,44 @@
         <v>2</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I60" s="11" t="s">
-        <v>146</v>
+        <v>197</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D61" t="s">
         <v>11</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F61" s="10">
         <v>3</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D62" t="s">
         <v>11</v>
@@ -2735,135 +2843,135 @@
         <v>2</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B63" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="C63" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="D63" t="s">
+        <v>27</v>
+      </c>
+      <c r="E63" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="F63" s="10">
+        <v>1</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I63" s="7" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" s="10" t="s">
         <v>151</v>
-      </c>
-      <c r="C63" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="D63" t="s">
-        <v>28</v>
-      </c>
-      <c r="E63" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="F63" s="10">
-        <v>1</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I63" s="7" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A64">
-        <v>59</v>
-      </c>
-      <c r="B64" s="10" t="s">
-        <v>155</v>
       </c>
       <c r="C64" s="11"/>
       <c r="D64" t="s">
         <v>23</v>
       </c>
       <c r="E64" s="10" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F64" s="10">
         <v>3</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I64" s="12" t="s">
-        <v>156</v>
+        <v>198</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C65" s="11"/>
       <c r="D65" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="F65" s="10">
         <v>1</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="D66" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="F66" s="10">
         <v>1</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I66" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D67" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E67" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="F67">
         <v>2</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="D68" t="s">
         <v>11</v>
@@ -2875,21 +2983,21 @@
         <v>2</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I68" s="10" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="D69" t="s">
         <v>11</v>
@@ -2901,45 +3009,45 @@
         <v>2</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I69" s="10" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D70" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E70" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F70" s="10">
         <v>2</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I70" s="10"/>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D71" t="s">
         <v>11</v>
@@ -2951,137 +3059,197 @@
         <v>3</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I71" s="10"/>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D72" t="s">
         <v>23</v>
       </c>
       <c r="E72" s="10" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F72" s="10"/>
       <c r="H72" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I72" s="10" t="s">
-        <v>174</v>
+        <v>199</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>176</v>
+        <v>139</v>
       </c>
       <c r="D73" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>177</v>
+        <v>12</v>
       </c>
       <c r="F73" s="10">
         <v>2</v>
       </c>
-      <c r="H73" s="1" t="s">
-        <v>69</v>
+      <c r="G73" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="I73" s="10" t="s">
-        <v>132</v>
+        <v>174</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>69</v>
-      </c>
-      <c r="B74" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="C74" s="11" t="s">
-        <v>142</v>
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>191</v>
+      </c>
+      <c r="C74" t="s">
+        <v>192</v>
       </c>
       <c r="D74" t="s">
-        <v>11</v>
-      </c>
-      <c r="E74" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F74" s="10">
-        <v>2</v>
+        <v>27</v>
+      </c>
+      <c r="E74" t="s">
+        <v>153</v>
+      </c>
+      <c r="F74">
+        <v>1</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I74" s="10" t="s">
-        <v>179</v>
+        <v>68</v>
+      </c>
+      <c r="I74" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B75" t="s">
+        <v>200</v>
+      </c>
+      <c r="C75" t="s">
         <v>201</v>
       </c>
-      <c r="C75" t="s">
+      <c r="D75" t="s">
+        <v>27</v>
+      </c>
+      <c r="E75" t="s">
+        <v>12</v>
+      </c>
+      <c r="F75">
+        <v>1</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
         <v>202</v>
       </c>
-      <c r="D75" t="s">
+      <c r="C76" t="s">
+        <v>203</v>
+      </c>
+      <c r="D76" t="s">
         <v>23</v>
       </c>
-      <c r="E75" t="s">
-        <v>158</v>
+      <c r="E76" t="s">
+        <v>153</v>
+      </c>
+      <c r="F76">
+        <v>2</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>213</v>
+      </c>
+      <c r="C77" t="s">
+        <v>204</v>
+      </c>
+      <c r="D77" t="s">
+        <v>23</v>
+      </c>
+      <c r="E77" t="s">
+        <v>153</v>
+      </c>
+      <c r="F77">
+        <v>2</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I77" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>77</v>
+      </c>
       <c r="B78" t="s">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="C78" t="s">
+        <v>206</v>
+      </c>
+      <c r="D78" t="s">
+        <v>27</v>
+      </c>
+      <c r="E78" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B79" t="s">
-        <v>181</v>
-      </c>
-      <c r="C79" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B80" t="s">
-        <v>182</v>
-      </c>
-      <c r="C80" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="81" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B81" t="s">
-        <v>183</v>
-      </c>
-      <c r="C81" t="s">
-        <v>24</v>
+      <c r="F78">
+        <v>1</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="85" spans="2:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="B85" t="s">
+        <v>209</v>
+      </c>
+      <c r="C85" t="s">
+        <v>153</v>
+      </c>
+      <c r="D85" t="s">
+        <v>177</v>
+      </c>
+      <c r="I85" s="18" t="s">
+        <v>210</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D75">
+  <conditionalFormatting sqref="D2:D78">
     <cfRule type="cellIs" dxfId="15" priority="8" operator="equal">
       <formula>"Not started"</formula>
     </cfRule>
@@ -3092,7 +3260,7 @@
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E75">
+  <conditionalFormatting sqref="E2:E78">
     <cfRule type="containsText" dxfId="12" priority="2" operator="containsText" text="Alle">
       <formula>NOT(ISERROR(SEARCH("Alle",E2)))</formula>
     </cfRule>
@@ -3137,7 +3305,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -3160,7 +3328,7 @@
         <v>5</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -3168,16 +3336,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="F3" s="10">
         <v>1</v>
@@ -3188,16 +3356,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="F4" s="10">
         <v>1</v>
@@ -3208,22 +3376,22 @@
         <v>3</v>
       </c>
       <c r="B5" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="F5" s="10">
+        <v>1</v>
+      </c>
+      <c r="G5" s="10" t="s">
         <v>121</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="F5" s="10">
-        <v>1</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -3231,13 +3399,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="F6" s="10">
         <v>1</v>
@@ -3248,19 +3416,19 @@
         <v>5</v>
       </c>
       <c r="B7" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="E7" s="10" t="s">
         <v>126</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>128</v>
       </c>
       <c r="F7" s="10">
         <v>3</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -3268,19 +3436,19 @@
         <v>6</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F8" s="10">
         <v>2</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -3288,19 +3456,19 @@
         <v>7</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="F9" s="10">
         <v>1</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -3308,10 +3476,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>12</v>
@@ -3320,7 +3488,7 @@
         <v>3</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -3328,10 +3496,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>12</v>
@@ -3340,7 +3508,7 @@
         <v>2</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -3348,10 +3516,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>12</v>
@@ -3360,7 +3528,7 @@
         <v>2</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -3368,19 +3536,19 @@
         <v>11</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E13" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="F13" s="10">
+        <v>2</v>
+      </c>
+      <c r="G13" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="F13" s="10">
-        <v>2</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -3388,13 +3556,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F14" s="10">
         <v>3</v>
@@ -3405,10 +3573,10 @@
         <v>13</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>24</v>
@@ -3422,13 +3590,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F16" s="10">
         <v>1</v>
@@ -3439,10 +3607,10 @@
         <v>15</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F17" s="10">
         <v>3</v>
@@ -3450,10 +3618,10 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B18" s="10" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="F18" s="10">
         <v>1</v>
@@ -3461,13 +3629,13 @@
     </row>
     <row r="19" spans="1:7" ht="30.75" x14ac:dyDescent="0.3">
       <c r="B19" s="13" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="F19" s="10">
         <v>1</v>
@@ -3475,7 +3643,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -3498,7 +3666,7 @@
         <v>5</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -3506,19 +3674,19 @@
         <v>1</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F24" s="10">
         <v>2</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -3526,13 +3694,13 @@
         <v>2</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F25" s="10">
         <v>2</v>
@@ -3543,13 +3711,13 @@
         <v>3</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F26" s="10">
         <v>2</v>
@@ -3560,10 +3728,10 @@
         <v>4</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>24</v>
@@ -3577,16 +3745,16 @@
         <v>5</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -3594,19 +3762,19 @@
         <v>6</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="F29" s="10">
         <v>2</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -3614,10 +3782,10 @@
         <v>7</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E30" s="10" t="s">
         <v>12</v>
